--- a/untitled folder/HSC_Physics_2nd_Paper_Chapter_10_Semiconductor_and_Electronics.xlsx
+++ b/untitled folder/HSC_Physics_2nd_Paper_Chapter_10_Semiconductor_and_Electronics.xlsx
@@ -1168,11 +1168,6 @@
           <t>বিচ্ছিন্ন একক পরমাণুর ক্ষেত্রে বিচ্ছিন্ন শক্তিস্তর (Discrete energy levels) থাকলেও কেলাসে পরমাণুগুলো কাছাকাছি এসে সন্নিবিষ্ট হলে শক্তি ব্যান্ড (Energy Bands) গঠিত হয় কেন? পাউলির অপবর্জন নীতির ভূমিকা ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>বিচ্ছিন্ন পরমাণুগুলোর মধ্যে কোনো পারস্পরিক মিথস্ক্রিয়া থাকে না। কিন্তু কেলাস গঠনের সময় যখন $N$ সংখ্যক পরমাণু পরস্পরের সন্নিকটে আসে (পারমাণবিক ব্যবধান $\sim\text{\AA}$), তখন প্রতিবেশী পরমাণুর শক্তিশালী কুলম্ব ক্ষেত্রে তাদের বহিস্থ ইলেকট্রনগুলোর তরঙ্গ ফাংশনের উপরিপাতন ঘটে। পাউলির অপবর্জন নীতি অনুসারে দুটি ইলেকট্রন একই কোয়ান্টাম অবস্থায় থাকতে পারে না। ফলে প্রতিটি একক পারমাণবিক স্তর বিভক্ত হয়ে $N$ সংখ্যক অত্যন্ত কাছাকাছি ব্যবধানযুক্ত অতি সূক্ষ্ম শক্তিস্তরে পরিণত হয়। $N \sim 10^{23}$ হওয়ায় এই স্তরগুলো মিলে একটি অবিচ্ছিন্ন 'শক্তি ব্যান্ড' গঠন করে।</t>
@@ -1216,11 +1211,6 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>যোজন ব্যান্ড (Valence Band), পরিবহন ব্যান্ড (Conduction Band) এবং নিষিদ্ধ শক্তি ফাঁক (Forbidden Energy Gap - $E_g$)-এর সংজ্ঞা দাও এবং এর ভিত্তিতে পরিবাহী, অর্ধপরিবাহী ও অন্তরকের তুলনা করো।</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1315,11 +1305,6 @@
           <t>তাপমাত্রা বৃদ্ধি করলে ধাতব পরিবাহীর রোধ বৃদ্ধি পায় কিন্তু বিশুদ্ধ অর্ধপরিবাহীর রোধ নাটকীয়ভাবে হ্রাস পায় কেন?</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>পরিবাহীতে মুক্ত ইলেকট্রনের ঘনত্ব ($n$) অত্যন্ত উচ্চ এবং তাপমাত্রার সাথে প্রায় অপরিবর্তিত থাকে; কিন্তু তাপমাত্রা বাড়লে ধাতব ল্যাটিসের পারমাণবিক কম্পন বৃদ্ধি পাওয়ায় ইলেকট্রনদের সংঘর্ষের হার বাড়ে এবং রিল্যাক্সেশন সময় $\tau$ হ্রাস পায়, ফলে রোধ বাড়ে ($\rho = \frac{m}{n e^2 \tau} \propto T$)। বিশুদ্ধ অর্ধপরিবাহীতে পরম শূন্যে পরিবহন ব্যান্ড সম্পূর্ণ খালি থাকে। তাপমাত্রা বাড়লে যোজন ব্যান্ডের সমযোজী বন্ধন ভেঙে ইলেকট্রন-হোল যুগল সৃষ্টি হয়, ফলে মুক্ত চার্জ ঘনত্ব সূচকীয় হারে বিপুল বৃদ্ধি পায় ($n \propto e^{-E_g / 2k_B T}$)। এই চার্জ ঘনত্ব বৃদ্ধিজনিত পরিবাহিতা বৃদ্ধি সংঘর্ষের প্রভাবকে বহুগুণে ছাপিয়ে যায়, ফলে রোধ দ্রুত হ্রাস পায় (ঋণাত্মক তাপমাত্রা সহগ, $\alpha &lt; 0$)।</t>
@@ -1365,11 +1350,6 @@
           <t>পরম শূন্য তাপমাত্রায় ($0\text{ K}$) একটি নিখুঁত বিশুদ্ধ সিলিকন বা জার্মেনিয়াম স্ফটিক কোন ধরনের পদার্থ হিসেবে আচরণ করে এবং কেন?</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>পরম শূন্য তাপমাত্রায় ($T = 0\text{ K}$) তাপীয় শক্তির মান শূন্য ($k_B T = 0$)। সিলিকন বা জার্মেনিয়ামের সমস্ত যোজ্যতা ইলেকট্রন তাদের চতুর্যোজী সমযোজী বন্ধনে (Covalent bonds) সম্পূর্ণভাবে আবদ্ধ থাকে। কোনো তাপীয় আন্দোলন না থাকায় একটি বন্ধনও ভাঙতে পারে না। ফলে যোজন ব্যান্ড সম্পূর্ণ পূর্ণ থাকে এবং পরিবহন ব্যান্ড সম্পূর্ণ শূন্য থাকে ($n = 0, p = 0$)। কোনো মুক্ত আধান বাহক না থাকায় স্ফটিকটি একটি নিখুঁত আদর্শ অন্তরক (Perfect Insulator) হিসেবে আচরণ করে।</t>
@@ -1415,11 +1395,6 @@
           <t>কক্ষ তাপমাত্রায় সিলিকন ($E_g \approx 1.1\text{ eV}$) এবং জার্মেনিয়াম ($E_g \approx 0.7\text{ eV}$)-এর মধ্যে আধুনিক সেমিকন্ডাক্টর শিল্পে সিলিকন অধিক জনপ্রিয় হওয়ার প্রধান দুটি কারণ কী?</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>(১) উচ্চতর তাপীয় স্থিতিশীলতা ও কম লিকেজ কারেন্ট: সিলিকনের ব্যান্ডগ্যাপ বৃহত্তর হওয়ায় কক্ষ তাপমাত্রায় তাপীয় ইলেকট্রন-হোল যুগল সৃষ্টির হার জার্মেনিয়াম অপেক্ষা হাজার গুণ কম, ফলে বিপরীত সম্পৃক্ত লিকেজ কারেন্ট ন্যানো-অ্যাম্পিয়ার ($\text{nA}$) স্তরে থাকে (জার্মেনিয়ামে মাইক্রো-অ্যাম্পিয়ার $\mu\text{A}$)। সিলিকন প্রায় $150^\circ\text{C}-200^\circ\text{C}$ পর্যন্ত কার্যকর থাকে (জার্মেনিয়াম $\sim 75^\circ\text{C}$)। (২) চমৎকার নিরোধক অক্সাইড স্তর ($\text{SiO}_2$): সিলিকনের ওপর তাপ প্রয়োগে অতি উচ্চমানের প্রাকৃতিক অন্তরক ডাই-ইলেকট্রিক সিলিকন ডাই-অক্সাইড ($\text{SiO}_2$) স্তর তৈরি হয় যা আইসি (IC) ফ্যাব্রিকেশনে অপরিহার্য।</t>
@@ -1465,11 +1440,6 @@
           <t>প্রত্যক্ষ ব্যান্ডগ্যাপ (Direct Bandgap, যেমন GaAs) এবং পরোক্ষ ব্যান্ডগ্যাপ (Indirect Bandgap, যেমন Si, Ge) সেমিকন্ডাক্টরের মধ্যে ব্যান্ড কাঠামোর পার্থক্য কী এবং LED তৈরিতে কেন সিলিকন ব্যবহৃত হয় না?</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>প্রত্যক্ষ ব্যান্ডগ্যাপে পরিবহন ব্যান্ডের সর্বনিম্ন শক্তি এবং যোজন ব্যান্ডের সর্বোচ্চ শক্তি তরঙ্গ ভেক্টরের একই মানে ($k$-স্থান) অবস্থান করে। ফলে একটি ইলেকট্রন কোনো ল্যাটিস কম্পন বা ফোনন (Phonon) ছাড়াই সরাসরি ফোটন নির্গমন করে হোলের সাথে মিলিত হতে পারে, যা দক্ষ আলো নিঃসরণ ঘটায়। কিন্তু সিলিকনে এই চরমবিন্দুগুলো ভিন্ন ভিন্ন $k$-তে অবস্থান করে। ফলে রিকম্বিনেশনের সময় ভরবেগ সংরক্ষণের জন্য একটি ফোনন (তাপ) নির্গত হতে হয়, যার কারণে শক্তি আলোর পরিবর্তে তাপে নষ্ট হয়। তাই সিলিকন দিয়ে কার্যকর LED তৈরি অসম্ভব।</t>
@@ -1703,11 +1673,6 @@
           <t>ডোপিং বলতে কী বোঝায়? চতুর্জোজী সিলিকনে পঞ্চযোজী (Pentavalent) এবং ত্রিযোজী (Trivalent) অপদ্রব্য মেশালে যথাক্রমে কোন ধরনের অর্ধপরিবাহী তৈরি হয়?</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>বিশুদ্ধ অর্ধপরিবাহীর পরিবাহিতা ব্যাপকভাবে বৃদ্ধি করার জন্য এতে নিয়ন্ত্রিত মাত্রায় অতি সূক্ষ্ম পরিমাণ (প্রতি দশ লক্ষ পরমাণুতে ১টি, $1\text{ ppm}$) উপযুক্ত অপদ্রব্য পরমাণু যোগ করার প্রক্রিয়াকে ডোপিং বলে। ফসফরাস, আর্সেনিক বা অ্যান্টিমনির মতো পঞ্চযোজী পরমাণু ডোপ করলে অতিরিক্ত পঞ্চম ইলেকট্রনটি মুক্ত হয়ে যায়, ফলে $n$-টাইপ অর্ধপরিবাহী (দাতা স্তর বা Donor) তৈরি হয়। বোরন, অ্যালুমিনিয়াম বা গ্যালিয়ামের মতো ত্রিযোজী অপদ্রব্য ডোপ করলে একটি ইলেকট্রনের ঘাটতির কারণে অতিরিক্ত হোল সৃষ্টি হয়, ফলে $p$-টাইপ অর্ধপরিবাহী (গ্রহীতা স্তর বা Acceptor) তৈরি হয়।</t>
@@ -1753,11 +1718,6 @@
           <t>অর্ধপরিবাহীর ভরক্রিয়া সূত্রটি (Law of Mass Action) লেখো এবং এর ভৌত তাৎপর্য কী? $n$-টাইপ ডোপিং করলে হোল ঘনত্বের কী পরিবর্তন ঘটে?</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>তাপীয় সাম্যাবস্থায় যেকোনো ডোপিং যুক্ত বা বিশুদ্ধ অর্ধপরিবাহীতে মুক্ত ইলেকট্রন ঘনত্ব ($n$) এবং হোল ঘনত্বের ($p$) গুণফল সর্বদা ধ্রুবক এবং তা সহজাত ঘনত্বের বর্গের সমান: $n \cdot p = n_i^2(T)$। এটি তাপমাত্রা ছাড়া ডোপিং ঘনত্বের ওপর সম্পূর্ণ স্বাধীন। যদি $n$-টাইপ ডোপিং করে ইলেকট্রন ঘনত্ব বিপুল পরিমাণে বৃদ্ধি করা হয় ($n \gg n_i$), তবে এই গুণফল বজায় রাখার জন্য অতিরিক্ত রিকম্বিনেশনের মাধ্যমে সংখ্যালঘু বাহক হোল ঘনত্ব ব্যাপকভাবে হ্রাস পায় ($p = \frac{n_i^2}{n} \ll n_i$)।</t>
@@ -1803,11 +1763,6 @@
           <t>একটি $n$-টাইপ অর্ধপরিবাহীতে কোটি কোটি মুক্ত ইলেকট্রন বিদ্যমান এবং $p$-টাইপে বিপুল সংখ্যক হোল রয়েছে। তা সত্ত্বেও একটি $n$-টাইপ বা $p$-টাইপ খণ্ড সামগ্রিকভাবে তড়িৎ-নিরপেক্ষ (Electrically Neutral) থাকে কেন?</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>ডোপিং প্রক্রিয়ায় যোগ করা অপদ্রব্য পরমাণুগুলো (যেমন P বা B) এবং সিলিকন পরমাণুগুলো নিজেরা চার্জহীন তড়িৎ-নিরপেক্ষ পরমাণু। $n$-টাইপে যখন একটি দাতা পরমাণু মুক্ত ইলেকট্রন দান করে, তখন দাতা পরমাণুটি নিজে একটি ধনাত্মক আয়নে ($N_d^+$) পরিণত হয় যা ল্যাটিসে স্থির থাকে। ফলে মোট ঋণাত্মক চার্জ (ইলেকট্রন) মোট ধনাত্মক চার্জের (স্থির দাতা আয়ন + সংখ্যালঘু হোল) হুবহু সমান হয়: $n = N_d^+ + p$। তাই সামগ্রিকভাবে স্ফটিকটির ওপর কোনো নিট বৈদ্যুতিক আধান থাকে না। একইভাবে $p$-টাইপে $p = N_a^- + n$ চার্জ নিরপেক্ষতা বজায় থাকে।</t>
@@ -1853,11 +1808,6 @@
           <t>$n$-টাইপ এবং $p$-টাইপ অর্ধপরিবাহীতে ফার্মি শক্তিস্তর $E_F$ সহজাত অবস্থান থেকে কোন দিকে সরে যায়?</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>$n$-টাইপ অর্ধপরিবাহীতে দাতা শক্তিস্তর ($E_d$) পরিবহন ব্যান্ডের ঠিক নিচে ($\sim 0.05\text{ eV}$) অবস্থান করে। মুক্ত ইলেকট্রনের ঘনত্ব বৃদ্ধি পাওয়ায় ইলেকট্রন থাকার সম্ভাব্যতা বৃদ্ধি পায়, ফলে ফার্মি স্তর $E_F$ উপরের দিকে উঠে পরিবহন ব্যান্ডের কাছাকাছি অবস্থান করে ($E_c$-এর নিকটে)। $p$-টাইপে গ্রহীতা শক্তিস্তর ($E_a$) যোজন ব্যান্ডের ঠিক উপরে অবস্থান করে। বিপুল হোল সৃষ্টির কারণে ফার্মি স্তর নিচের দিকে নেমে যোজন ব্যান্ডের কাছাকাছি অবস্থান করে ($E_v$-এর নিকটে)।</t>
@@ -1903,11 +1853,6 @@
           <t>মুক্ত ইলেকট্রন ঘনত্ব $n$, হোল ঘনত্ব $p$, ইলেকট্রন গতিশীলতা $\mu_n$ এবং হোল গতিশীলতা $\mu_p$ হলে অর্ধপরিবাহীর মোট পরিবাহিতা $\sigma$ এবং রোধকত্ব $\rho$-এর সমীকরণটি কী?</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>অর্ধপরিবাহীতে তড়িৎ প্রবাহ ইলেকট্রন ও হোল উভয়ের গতির যোগফল: $J = J_n + J_p = (n e v_n + p e v_p) = e (n \mu_n + p \mu_p) E$। ওহমের সূত্র $J = \sigma E$ থেকে পরিবাহিতা: $\sigma = e (n \mu_n + p \mu_p)$। রোধকত্ব হলো পরিবাহিতার বিপরীত রাশি: $\rho = \frac{1}{\sigma} = \frac{1}{e (n \mu_n + p \mu_p)}$। সহজাত অবস্থায় $n = p = n_i$ বসালে $\sigma_i = n_i e (\mu_n + \mu_p)$।</t>
@@ -1953,11 +1898,6 @@
           <t>কক্ষ তাপমাত্রায় সিলিকনের সহজাত ঘনত্ব $n_i = 1.5 \times 10^{10}\text{ cm}^{-3}$। একটি সিলিকন স্ফটিকে $N_d = 1.0 \times 10^{16}\text{ cm}^{-3}$ ফসফরাস ডোপ করা হলে সংখ্যাগুরু ইলেকট্রন ঘনত্ব এবং সংখ্যালঘু হোল ঘনত্ব কত হবে?</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>সম্পূর্ণ আয়ননে সংখ্যাগুরু ইলেকট্রন ঘনত্ব দাতা ঘনত্বের সমান: $n \approx N_d = 1.0 \times 10^{16}\text{ cm}^{-3}$। ভরক্রিয়া সূত্রানুযায়ী: $p = \frac{n_i^2}{n} = \frac{(1.5 \times 10^{10})^2}{1.0 \times 10^{16}} = \frac{2.25 \times 10^{20}}{1.0 \times 10^{16}} = 2.25 \times 10^4\text{ cm}^{-3}$। অর্থাৎ ইলেকট্রন ঘনত্ব হোলের চেয়ে প্রায় $10^{12}$ গুণ বেশি।</t>
@@ -2003,11 +1943,6 @@
           <t>হল প্রভাব কী? হল সহগ (Hall Coefficient) $R_H$-এর চিহ্নের মাধ্যমে কীভাবে একটি অজ্ঞাত সেমিকন্ডাক্টর $n$-টাইপ নাকি $p$-টাইপ তা নিশ্চিতভাবে শনাক্ত করা যায়?</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>একটি তড়িৎবাহী সেমিকন্ডাক্টর পাতের ওপর লম্বভাবে চৌম্বক ক্ষেত্র $\vec{B}$ প্রয়োগ করলে লরেন্টজ বলের ($\vec{F} = q(\vec{v} \times \vec{B})$) কারণে চার্জ বাহকগুলো পাতের একপাশে জমা হয়, ফলে একটি অনুপ্রস্থ বিভব পার্থক্য (Hall Voltage, $V_H$) সৃষ্টি হয়; একে হল প্রভাব বলে। হল সহগ $R_H = \frac{1}{q n}$। $n$-টাইপ সেমিকন্ডাক্টরে চার্জ বাহক ইলেকট্রন ($q = -e$) হওয়ায় হল ভোল্টেজ ও হল সহগ ঋণাত্মক ($R_H &lt; 0$) হয়। $p$-টাইপে বাহক হোল ($q = +e$) হওয়ায় হল ভোল্টেজ ও হল সহগ ধনাত্মক ($R_H &gt; 0$) হয়।</t>
@@ -2053,11 +1988,6 @@
           <t>একটি ডোপড অর্ধপরিবাহীর তাপমাত্রার পরিবর্তনের সাথে চার্জ ঘনত্ব পরিবর্তনের তিনটি অঞ্চল (Freeze-out, Extrinsic/Saturation, এবং Intrinsic region) সংক্ষেপে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>(১) ফ্রিজ-আউট অঞ্চল (অতি নিম্ন তাপমাত্রা, $T &lt; 100\text{ K}$): তাপীয় শক্তি কম থাকায় অপদ্রব্য পরমাণুগুলো সম্পূর্ণ আয়নিত হতে পারে না, ইলেকট্রনগুলো দাতা স্তরে জমে থাকে। (২) স্যাচুরেশন অঞ্চল (কক্ষ তাপমাত্রা, $100\text{ K} - 450\text{ K}$): সমস্ত অপদ্রব্য আয়নিত হয়ে যায় ($n \approx N_d$), ফলে তাপমাত্রা বাড়লেও চার্জ ঘনত্ব প্রায় স্থির থাকে (সেমিকন্ডাক্টর ডিভাইসের স্বাভাবিক কাজের অঞ্চল)। (৩) সহজাত অঞ্চল (অতি উচ্চ তাপমাত্রা, $T &gt; 500\text{ K}$): সমযোজী বন্ধন ব্যাপকভাবে ভাঙতে শুরু করায় তাপীয় বাহক ঘনত্ব অপদ্রব্য ঘনত্বকে বহুগুণে ছাড়িয়ে যায় ($n_i \gg N_d$), ফলে ডিভাইসটি তার $n$ বা $p$ বৈশিষ্ট্য হারিয়ে বিশুদ্ধ অর্ধপরিবাহীর মতো আচরণ করে অকেজো হয়ে পড়ে।</t>
@@ -2103,11 +2033,6 @@
           <t>বিশুদ্ধ সিলিকনের রোধকত্ব প্রায় $2.3 \times 10^3\ \Omega\cdot\text{m}$। মাত্র $1\text{ ppm}$ ডোপিং করলে এর রোধকত্ব কীভাবে লক্ষ গুণ হ্রাস পেয়ে প্রায় $10^{-3}\ \Omega\cdot\text{m}$-এ নেমে আসে?</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>সিলিকনের পারমাণবিক ঘনত্ব প্রায় $5 \times 10^{22}\text{ atoms/cm}^3$। মাত্র $1\text{ ppm}$ ডোপিং-এর অর্থ প্রতি দশ লক্ষ সিলিকনে ১টি অপদ্রব্য, যার ঘনত্ব $N_d = 5 \times 10^{16}\text{ cm}^{-3}$। যেখানে বিশুদ্ধ সিলিকনে মুক্ত বাহক ছিল মাত্র $n_i \approx 1.5 \times 10^{10}\text{ cm}^{-3}$, সেখানে ডোপিং-এর ফলে বাহক ঘনত্ব এক ধাক্কায় প্রায় ৩০ লক্ষ গুণ বৃদ্ধি পায় ($n \approx N_d$)! যেহেতু রোধকত্ব $\rho \propto \frac{1}{n}$, তাই বাহক ঘনত্ব কোটিগুণ বাড়ায় রোধকত্ব কয়েক লক্ষ গুণ হ্রাস পেয়ে চমৎকার পরিবাহীতে পরিণত হয়।</t>
@@ -2153,11 +2078,6 @@
           <t>একটি $p-n$ জংশন গঠিত হওয়ার মুহূর্তে ডিপলেশন অঞ্চল (Depletion Region) এবং অন্তর্নির্মিত বিভব প্রাচীর (Built-in Potential - $V_{bi}$) কীভাবে স্বতঃস্ফূর্তভাবে সৃষ্টি হয়?</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>জংশন তৈরির সাথে সাথে ঘনত্বের পার্থক্যের কারণে $n$-অঞ্চল থেকে ইলেকট্রন $p$-অঞ্চলে এবং $p$-অঞ্চল থেকে হোল $n$-অঞ্চলে ব্যাপিত (Diffusion) হয়। সংযোগস্থলের কাছাকাছি এরা পরস্পর বিলীন (Recombine) হয়ে যায়। এর ফলে জংশনের $n$-পাশে অনড় ধনাত্মক দাতা আয়ন ($N_d^+$) এবং $p$-পাশে অনড় ঋণাত্মক গ্রহীতা আয়ন ($N_a^-$)-এর একটি মুক্ত চার্জহীন অঞ্চল তৈরি হয় যাকে ডিপলেশন স্তর বলে। এই উন্মুক্ত স্থির চার্জগুলো $n$ থেকে $p$-এর দিকে একটি অভ্যন্তরীণ বৈদ্যুতিক ক্ষেত্র ($\vec{E}$) সৃষ্টি করে, যার ফলে একটি বিভব বাধা ($V_{bi}$) তৈরি হয় যা পরবর্তী ব্যাপন প্রবাহ সম্পূর্ণ বন্ধ করে দেয়।</t>
@@ -2203,11 +2123,6 @@
           <t>তাপীয় সাম্যাবস্থায় $p-n$ জংশনের অন্তর্নির্মিত বিভব $V_{bi}$-এর সমীকরণটি $N_a, N_d,$ এবং $n_i$-এর মাধ্যমে প্রকাশ করো এবং সিলিকন জংশনের ক্ষেত্রে এর সাধারণ মান কত?</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>আইনস্টাইন সম্পর্ক ও বোল্টজম্যান বন্টন প্রয়োগ করে প্রতিপাদিত সমীকরণ: $V_{bi} = \frac{k_B T}{e} \ln\left(\frac{N_a N_d}{n_i^2}\right) = V_T \ln\left(\frac{N_a N_d}{n_i^2}\right)$, যেখানে $V_T = \frac{k_B T}{e} \approx 26\text{ mV}$ (কক্ষ তাপমাত্রায় তাপীয় বিভব)। সাধারণ সিলিকন ডায়োডের জন্য ($N_a \approx 10^{16}, N_d \approx 10^{16}, n_i \approx 1.5 \times 10^{10}$): $V_{bi} \approx 0.026 \times \ln(4.44 \times 10^{11}) \approx 0.026 \times 26.8 \approx 0.70\text{ V}$। জার্মেনিয়ামের ক্ষেত্রে $V_{bi} \approx 0.30\text{ V}$।</t>
@@ -2253,11 +2168,6 @@
           <t>$p-n$ জংশনে সম্মুখ বায়াস (Forward Bias) প্রয়োগ করলে ডিপলেশন স্তরের বেধ, বিভব প্রাচীরের উচ্চতা এবং তড়িৎ প্রবাহের কী পরিবর্তন ঘটে?</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>সম্মুখ বায়াসে ব্যাটারির ধনাত্মক প্রান্ত $p$-অঞ্চলে এবং ঋণাত্মক প্রান্ত $n$-অঞ্চলে যুক্ত করা হয়। প্রয়োগকৃত বাহ্যিক ভোল্টেজ $V$ অভ্যন্তরীণ অন্তর্নির্মিত ক্ষেত্রের বিপরীত হওয়ায় নিট বিভব প্রাচীর হ্রাস পেয়ে $(V_{bi} - V)$ হয়। কার্যকর বাধা কমে যাওয়ায় ডিপলেশন স্তর অত্যন্ত সংকীর্ণ ও পাতলা হয়ে যায়। যখন বাহ্যিক ভোল্টেজ কাট-ইন বিভব ($0.7\text{ V}$) অতিক্রম করে, তখন সংখ্যাগুরু বাহকগুলোর জন্য বাধা বিলুপ্ত হয় এবং তারা বিপুল সংখ্যায় জংশন অতিক্রম করে সূচকীয় হারে তীব্র সম্মুখ তড়িৎ প্রবাহ ($I \sim\text{mA}$) তৈরি করে।</t>
@@ -2303,11 +2213,6 @@
           <t>$p-n$ জংশনে বিপরীত বায়াস (Reverse Bias) প্রয়োগ করলে ডিপলেশন স্তর প্রশস্ত হয় কেন এবং এই অবস্থায় অতি ক্ষুদ্র বিপরীত সম্পৃক্ত প্রবাহ ($I_0$) প্রবাহিত হওয়ার কারণ কী?</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>বিপরীত বায়াসে $p$-অঞ্চলে ব্যাটারির ঋণাত্মক এবং $n$-অঞ্চলে ধনাত্মক প্রান্ত যুক্ত করা হয়। এটি অভ্যন্তরীণ ক্ষেত্রের অনুকূলে কাজ করে নিট বিভব প্রাচীর বৃদ্ধি করে $(V_{bi} + V)$ করে। সংখ্যাগুরু বাহকগুলো জংশন থেকে দূরে সরে যাওয়ায় ডিপলেশন স্তর আরও প্রশস্ত হয় এবং সংখ্যাগুরু প্রবাহ সম্পূর্ণ বন্ধ হয়ে যায়। তবে তাপীয় উত্তেজনার ফলে জংশনের নিকটে সৃষ্টি হওয়া সংখ্যালঘু বাহকগুলো (যেমন $p$-অঞ্চলের ইলেকট্রন ও $n$-অঞ্চলের হোল) এই উচ্চ বৈদ্যুতিক ক্ষেত্র দ্বারা সহজে জংশন পার হয়ে যায়, যার ফলে একটি অতি ক্ষুদ্র ($I_0 \sim\text{nA}$ বা $\mu\text{A}$) ভোল্টেজ-স্বাধীন 'বিপরীত সম্পৃক্ত প্রবাহ' প্রবাহিত হয়।</t>
@@ -2404,11 +2309,6 @@
           <t>একটি সিলিকন ডায়োডের সম্মুখ বায়াসে অপারেটিং পয়েন্টে কারেন্ট $I = 26\text{ mA}$ হলে কক্ষ তাপমাত্রায় ($T = 300\text{ K}$) এর গতিশীল বা এসি রোধ $r_d$ কত? ($\eta = 1$)</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>শক্লি সমীকরণ ব্যবকলন করে গতিশীল রোধ পাওয়া যায়: $r_d = \frac{dV}{dI} = \frac{\eta V_T}{I + I_0} \approx \frac{\eta V_T}{I}$। কক্ষ তাপমাত্রায় তাপীয় বিভব $V_T = 26\text{ mV}$। মান বসিয়ে: $r_d = \frac{1 \times 26\text{ mV}}{26\text{ mA}} = \frac{26 \times 10^{-3}\text{ V}}{26 \times 10^{-3}\text{ A}} = 1.0\ \Omega$। অর্থাৎ সম্মুখ বায়াসে পর্যাপ্ত কারেন্টে ডায়োডের গতিশীল রোধ অত্যন্ত ক্ষুদ্র ($\approx 1\ \Omega$) হয়।</t>
@@ -2454,11 +2354,6 @@
           <t>বিপরীত বায়াসে জেনার ব্রেকডাউন (Zener Breakdown) এবং অ্যাভালাঞ্চ ব্রেকডাউন (Avalanche Breakdown)-এর মধ্যে ডোপিং মাত্রা ও ভৌত মেকানিজমের মূল পার্থক্য কী?</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>(১) জেনার ব্রেকডাউন: অত্যন্ত ভারী ডোপিংযুক্ত ($&gt; 1:10^4$) ডায়োডে ঘটে যেখানে ডিপলেশন স্তর অতি পাতলা ($\sim 10\text{ nm}$) হয়। ফলে তুলনামূলক কম বিপরীত ভোল্টেজেই ($V_Z &lt; 5-6\text{ V}$) প্রচণ্ড বৈদ্যুতিক ক্ষেত্র ($\sim 10^7\text{ V/m}$) সৃষ্টি হয় যা সরাসরি সমযোজী বন্ধন ছিঁড়ে কোয়ান্টাম টানেলিং-এর মাধ্যমে ইলেকট্রন মুক্ত করে। (২) অ্যাভালাঞ্চ ব্রেকডাউন: হালকা ডোপিংযুক্ত ডায়োডে ঘটে যেখানে ডিপলেশন স্তর প্রশস্ত হয়। উচ্চ বিপরীত ভোল্টেজে ($V_{BR} &gt; 6-8\text{ V}$) দ্রুতগামী সংখ্যালঘু বাহকগুলো সংঘর্ষের মাধ্যমে পরমাণু থেকে নতুন ইলেকট্রন-হোল তৈরি করে যা তুষারপাতের মতো গুণিতক হারে (Impact Ionization) কারেন্ট বৃদ্ধি করে।</t>
@@ -2504,11 +2399,6 @@
           <t>$p-n$ জংশনের উভয় পাশে ডোপিং ঘনত্ব বৃদ্ধি করলে ডিপলেশন স্তরের বেধ $W$-এর কী পরিবর্তন ঘটে এবং কেন?</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>ডিপলেশন স্তরের বেধের সমীকরণ: $W = \sqrt{\frac{2\epsilon}{e}\left(\frac{1}{N_a} + \frac{1}{N_d}\right)(V_{bi} - V)}$। এই সমীকরণ স্পষ্টভাবে নির্দেশ করে যে ডোপিং ঘনত্ব $N_a$ ও $N_d$ যত বৃদ্ধি পায়, ডিপলেশন স্তরের বেধ $W$ তত হ্রাস পায়। কারণ উচ্চ ডোপিংযুক্ত অঞ্চলে অল্প দূরত্বের মধ্যেই প্রয়োজনীয় সংখ্যক উন্মুক্ত আয়ন পাওয়া যায় যা বিপরীত অঞ্চলকে সন্তুষ্ট করতে যথেষ্ট। তাই ভারী ডোপিং-এ ডিপলেশন স্তর অত্যন্ত সংকীর্ণ ($&lt; 0.1\ \mu\text{m}$) হয়।</t>
@@ -2554,11 +2444,6 @@
           <t>$p-n$ জংশনের ট্রানজিশন বা ডিপলেশন ধারকত্ব ($C_T$) এবং ডিফিউশন বা ব্যাপন ধারকত্ব ($C_D$) কোন কোন বায়াসিং অবস্থায় প্রধান ভূমিকা পালন করে?</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>(১) ট্রানজিশন ক্যাপাসিট্যান্স ($C_T$): বিপরীত বায়াসে প্রধান ভূমিকা রাখে। ডিপলেশন স্তরের অপরিবাহী অঞ্চলের দুই পাশে $p$ ও $n$ অঞ্চলের চার্জিত স্তর একটি সমান্তরাল পাত ধারকের মতো আচরণ করে: $C_T = \frac{\epsilon A}{W} \propto \frac{1}{\sqrt{V_{bi} + V_R}}$। (২) ডিফিউশন ক্যাপাসিট্যান্স ($C_D$): সম্মুখ বায়াসে প্রধান ভূমিকা পালন করে। এটি জংশন অতিক্রমকারী সংখ্যালঘু চার্জ বাহক সঞ্চয়ের কারণে সৃষ্টি হয় এবং এটি সম্মুখ কারেন্টের সমানুপাতিক ($C_D \propto I_F$)। উচ্চ কম্পাঙ্কের এসি সার্কিটে এই ধারকত্ব ডায়োডের সুইচিং গতিকে সীমিত করে।</t>
@@ -2604,11 +2489,6 @@
           <t>উচ্চ কম্পাঙ্কের ডিজিটাল সুইচিং সার্কিটে একটি সাধারণ $p-n$ ডায়োড সম্মুখ বায়াস থেকে হঠাৎ বিপরীত বায়াসে নিলে সাথে সাথে বন্ধ না হয়ে কিছু সময়ের জন্য বিপরীত কারেন্ট প্রবাহিত করে কেন?</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>সম্মুখ বায়াস চলাকালীন বিপুল সংখ্যক সংখ্যালঘু বাহক জংশনের উভয় পাশে ব্যাপিত হয়ে সঞ্চিত অবস্থায় থাকে (Stored charge)। যখন হঠাৎ বিপরীত বায়াস প্রয়োগ করা হয়, তখন এই সঞ্চিত সংখ্যালঘু বাহকগুলো অবিলম্বে উধাও হতে পারে না; পুনরায় বিপরীত দিকে টেনে তাদের সম্পূর্ণ অপসারণ বা রিকম্বিনেশন করতে একটি সসীম সময় লাগে। এই সময়কে রিভার্স রিকভারি সময় ($t_{rr}$) বলে। এই সময়ে ডায়োডটি বিপরীত দিকে মারাত্মক লিকেজ কারেন্ট পরিচালনা করে। উচ্চগতির জন্য শর্টকি ডায়োড ব্যবহৃত হয়।</t>
@@ -2654,11 +2534,6 @@
           <t>একটি অর্ধ-তরঙ্গ রেকটিফায়ার (Half-Wave Rectifier)-এ এসি ইনপুটের কম্পাঙ্ক $f$ হলে আউটপুট রিপল কম্পাঙ্ক কত এবং এর সর্বোচ্চ তাত্ত্বিক রূপান্তর দক্ষতা $\eta_{\max}$ কত শতাংশ?</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>অর্ধ-তরঙ্গ রেকটিফায়ারে এসি ইনপুটের প্রতি পূর্ণ চক্রের কেবল ধনাত্মক অর্ধ-চক্রে ডায়োড অন হয় এবং ঋণাত্মক অর্ধ-চক্রে অফ থাকে। ফলে আউটপুট স্পন্দনের পর্যায়কাল ইনপুটের পর্যায়কালের সমান থাকে, অর্থাৎ রিপল কম্পাঙ্ক $f_{\text{ripple}} = f$ (ইনপুট ৫০ হার্জ হলে আউটপুট ৫০ হার্জ)। সর্বোচ্চ তাত্ত্বিক দক্ষতা: $\eta = \frac{P_{dc}}{P_{ac}} = \frac{(I_m / \pi)^2 R_L}{(I_m / 2)^2 (R_L + r_d)} \approx \frac{4}{\pi^2} \approx 40.6\%$।</t>
@@ -2704,11 +2579,6 @@
           <t>পূর্ণ-তরঙ্গ সেন্টার-ট্যাপড এবং ব্রিজ রেকটিফায়ারের রিপল কম্পাঙ্ক কত এবং এদের সর্বোচ্চ তাত্ত্বিক দক্ষতা কত? ব্রিজ রেকটিফায়ারের প্রধান সুবিধা কী?</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>পূর্ণ-তরঙ্গ রেকটিফায়ারে এসি ইনপুটের উভয় অর্ধ-চক্রেই কারেন্ট লোডের মধ্য দিয়ে একই দিকে প্রবাহিত হয়। ফলে আউটপুট রিপল কম্পাঙ্ক ইনপুট কম্পাঙ্কের দ্বিগুণ হয়: $f_{\text{ripple}} = 2f$ (৫০ হার্জ ইনপুটে ১০০ হার্জ রিপল)। সর্বোচ্চ রূপান্তর দক্ষতা অর্ধ-তরঙ্গের দ্বিগুণ: $\eta_{\max} = \frac{8}{\pi^2} \approx 81.2\%$। ব্রিজ রেকটিফায়ারে কোনো ভারী ও ব্যয়বহুল সেন্টার-ট্যাপড ট্রান্সফরমার প্রয়োজন হয় না এবং এর পিক ইনভার্স ভোল্টেজ ($PIV = V_m$) সেন্টার-ট্যাপের ($2V_m$) অর্ধেক হয়।</t>
@@ -2754,11 +2624,6 @@
           <t>পিক ইনভার্স ভোল্টেজ (PIV) বলতে কী বোঝায়? এসি ইনপুটের পিক মান $V_m$ হলে অর্ধ-তরঙ্গ, পূর্ণ-তরঙ্গ সেন্টার-ট্যাপ এবং ব্রিজ রেকটিফায়ারে ডায়োডের প্রয়োজনীয় ন্যূনতম PIV কত?</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>PIV হলো বিপরীত বায়াস অবস্থায় ডায়োডের দুই প্রান্তে প্রযুক্ত সম্ভাব্য সর্বোচ্চ পিক ভোল্টেজ যা ডায়োডকে নষ্ট (ব্রেকডাউন) না করে সহ্য করতে হয়। (১) অর্ধ-তরঙ্গ রেকটিফায়ার: $PIV = V_m$। (২) সেন্টার-ট্যাপড পূর্ণ-তরঙ্গ রেকটিফায়ার: $PIV = 2V_m$ (কারণ বিপরীত চক্রে অফ ডায়োডের প্রান্তে সম্পূর্ণ সেকেন্ডারির দ্বিগুণ ভোল্টেজ পড়ে)। (৩) ব্রিজ রেকটিফায়ার: $PIV = V_m$।</t>
@@ -2804,11 +2669,6 @@
           <t>রেকটিফায়ারের রিপল ফ্যাক্টর ($\gamma$) বলতে কী বোঝায় এবং ফিল্টারহীন অবস্থায় অর্ধ-তরঙ্গ ও পূর্ণ-তরঙ্গ রেকটিফায়ারের রিপল ফ্যাক্টরের মান কত?</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>রিপল ফ্যাক্টর হলো আউটপুটে উপস্থিত এসি উপাদানের কার্যকর (rms) মান এবং ডিসি উপাদানের মানের অনুপাত: $\gamma = \frac{V_{ac,\text{rms}}}{V_{dc}} = \sqrt{\left(\frac{V_{\text{rms}}}{V_{dc}}\right)^2 - 1}$। এটি আউটপুট ডিসির বিশুদ্ধতা নির্দেশ করে। অর্ধ-তরঙ্গ রেকটিফায়ারে $\gamma = \sqrt{\left(\frac{V_m/2}{V_m/\pi}\right)^2 - 1} = \sqrt{\frac{\pi^2}{4} - 1} \approx 1.21$ (বা ১২১%)। পূর্ণ-তরঙ্গ রেকটিফায়ারে $\gamma = \sqrt{\left(\frac{V_m/\sqrt{2}}{2V_m/\pi}\right)^2 - 1} = \sqrt{\frac{\pi^2}{8} - 1} \approx 0.482$ (বা ৪৮.২%)।</t>
@@ -2854,11 +2714,6 @@
           <t>রেকটিফায়ারের আউটপুটে লোড রোধের সমান্তরালে একটি বৃহৎ ধারক ($C$) যুক্ত করলে রিপল কীভাবে নাটকীয়ভাবে হ্রাস পায় এবং আউটপুট ডিসি ভোল্টেজ কেন পিক মানের ($V_m$) কাছাকাছি থাকে?</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>ডায়োড যখন অন হয়, তখন ধারকটি দ্রুত পিক ভোল্টেজ $V_m$ পর্যন্ত চার্জিত হয়। যখন ইনপুট ভোল্টেজ পিক থেকে কমতে শুরু করে, ডায়োডটি রিভার্স বায়াস হয়ে অফ হয়ে যায়। তখন ধারকটি লোড রোধ $R_L$-এর মধ্য দিয়ে খুব ধীরে ধীরে ডিসচার্জ হতে থাকে ($RC \gg T$ হলে)। পরবর্তী পিক আসার পূর্বেই ধারক তার ভোল্টেজ ধরে রাখে, ফলে আউটপুট ভোল্টেজ শূন্যে না নেমে প্রায় ধ্রুব $V_m$-এর কাছাকাছি সমতল থাকে। রিপল ভোল্টেজ দাঁড়ায় $V_r \approx \frac{I_{dc}}{2 f C}$।</t>
@@ -2904,11 +2759,6 @@
           <t>একটি জেনার ডায়োডকে কীভাবে ডিসি ভোল্টেজ নিয়ন্ত্রক (Voltage Regulator) হিসেবে ব্যবহার করা হয় এবং এটিকে সর্বদা কোন বায়াসে যুক্ত করতে হয়?</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>জেনার ডায়োডকে সর্বদা বিপরীত বায়াসে (Reverse Breakdown region) এবং লোড রোধের সমান্তরালে যুক্ত করা হয়। এর সাথে সিরিজে একটি সুরক্ষামূলক ড্রপিং রোধ $R_S$ থাকে। জেনার ব্রেকডাউন অঞ্চলে ডায়োডের মধ্য দিয়ে প্রবাহিত কারেন্ট ব্যাপক পরিবর্তিত হলেও এর দুই প্রান্তের ভোল্টেজ কার্যত সম্পূর্ণ স্থির বা ধ্রুব ($V_Z$) থাকে। ফলে অনিয়ন্ত্রিত ইনপুট ভোল্টেজ বৃদ্ধি পেলে অতিরিক্ত ভোল্টেজ ড্রপ হয় সিরিজ রোধ $R_S$-এ এবং লোডের দুই প্রান্তে সর্বদা সুনির্দিষ্ট ধ্রুব ভোল্টেজ $V_Z$ বজায় থাকে।</t>
@@ -2954,11 +2804,6 @@
           <t>একটি $V_Z = 10\text{ V}$ জেনার ডায়োড $V_{\text{in}} = 15\text{ V}$ অনিয়ন্ত্রিত সরবরাহ থেকে $R_L = 1000\ \Omega$ লোডে ভোল্টেজ নিয়ন্ত্রণ করছে। জেনার কারেন্ট $I_Z = 15\text{ mA}$ রাখতে সিরিজ রোধ $R_S$-এর মান কত হওয়া উচিত?</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>লোড ভোল্টেজ $V_L = V_Z = 10\text{ V}$। লোড কারেন্ট $I_L = \frac{V_L}{R_L} = \frac{10\text{ V}}{1000\ \Omega} = 10\text{ mA}$। মোট সরবরাহ কারেন্ট $I_S = I_Z + I_L = 15\text{ mA} + 10\text{ mA} = 25\text{ mA}$। সিরিজ রোধের দুই প্রান্তে ভোল্টেজ ড্রপ $V_{RS} = V_{\text{in}} - V_Z = 15\text{ V} - 10\text{ V} = 5\text{ V}$। অতএব সিরিজ রোধ $R_S = \frac{V_{RS}}{I_S} = \frac{5\text{ V}}{25 \times 10^{-3}\text{ A}} = 200\ \Omega$।</t>
@@ -3004,11 +2849,6 @@
           <t>একটি জেনার ডায়োডের ব্রেকডাউন ভোল্টেজ $V_Z = 6.0\text{ V}$ এবং সর্বোচ্চ নিরাপদ ক্ষমতা অপচয় $P_{Z,\max} = 600\text{ mW}$। ডায়োডটি নষ্ট না হয়ে সর্বোচ্চ কত জেনার কারেন্ট $I_{Z,\max}$ বহন করতে পারে?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>জেনার ক্ষমতা অপচয় সমীকরণ: $P_Z = V_Z I_Z$। অতএব সর্বোচ্চ নিরাপদ জেনার কারেন্ট $I_{Z,\max} = \frac{P_{Z,\max}}{V_Z} = \frac{600 \times 10^{-3}\text{ W}}{6.0\text{ V}} = 0.1\text{ A} = 100\text{ mA}$। এর চেয়ে বেশি কারেন্ট প্রবাহিত হলে অতিরিক্ত তাপে ডায়োডের জংশন গলে নষ্ট হয়ে যাবে।</t>
@@ -3054,11 +2894,6 @@
           <t>ইলেকট্রনিক্সে ডায়োড ক্লিপার (Clipper) এবং ক্ল্যাম্পার (Clamper) সার্কিটের মূল কাজের পার্থক্য কী?</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>ক্লিপার (বা লিমিটার): একটি তরঙ্গরূপের (Waveform) নির্দিষ্ট অংশের আকার বা পিককে কেটে বাদ দেয় (Clip করে) কিন্তু বাকি অংশকে অবিকৃত রাখে; এটি মূলত ভোল্টেজের বিস্তার সীমাবদ্ধ করতে ব্যবহৃত হয়। ক্ল্যাম্পার (বা ডিসি রিস্টোরার): তরঙ্গরূপের কোনো অংশ না কেটে সম্পূর্ণ তরঙ্গটিকে ডিসি স্তরে উপরে বা নিচে স্থানান্তরিত করে (তরঙ্গের পিক-টু-পিক বিস্তার অপরিবর্তিত রেখে কেবল রেফারেন্স ডিসি লেভেল পরিবর্তন করে)।</t>
@@ -3104,11 +2939,6 @@
           <t>ডায়োড এবং ধারক সমন্বয়ে গঠিত 'ভোল্টেজ ডাবলার' (Voltage Doubler) সার্কিট কীভাবে কোনো ট্রান্সফরমার ছাড়াই পিক ইনপুটের দ্বিগুণ ($2V_m$) ডিসি ভোল্টেজ উৎপন্ন করে?</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>ভোল্টেজ ডাবলারে দুটি ডায়োড ও দুটি ধারক পর্যায়ক্রমে কাজ করে। ইনপুটের এক অর্ধ-চক্রে প্রথম ডায়োড দিয়ে প্রথম ধারকটি পিক মান $V_m$ পর্যন্ত চার্জিত হয়। বিপরীত অর্ধ-চক্রে এসি ইনপুট ভোল্টেজ এবং প্রথম ধারকের সঞ্চিত ভোল্টেজ সিরিজে যুক্ত হয়ে দ্বিতীয় ধারককে দ্বিতীয় ডায়োডের মাধ্যমে প্রায় $V_m + V_m = 2V_m$ পর্যন্ত চার্জ করে। আউটপুট নেওয়া হয় দ্বিতীয় ধারকের দুই প্রান্ত থেকে, ফলে ট্রান্সফরমার ছাড়াই দ্বিগুণ ডিসি ভোল্টেজ পাওয়া যায়।</t>
@@ -3154,11 +2984,6 @@
           <t>লাইট এমিটিং ডায়োড (LED) কোন বায়াসে কাজ করে এবং এতে আলো কীভাবে উৎপন্ন হয়? নির্গত আলোর বর্ণ কিসের ওপর নির্ভর করে?</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>LED সর্বদা সম্মুখ বায়াসে (Forward bias) চালিত হয়। সম্মুখ বায়াসে $n$-অঞ্চল থেকে ইলেকট্রন এবং $p$-অঞ্চল থেকে হোল জংশনে প্রবেশ করে। জংশন অঞ্চলে পরিবাহী ব্যান্ডের ইলেকট্রনগুলো যোজন ব্যান্ডের হোলের সাথে মিলিত (Recombine) হয়। প্রত্যক্ষ ব্যান্ডগ্যাপের উপাদানে ইলেকট্রন উচ্চ শক্তিস্তর থেকে নিম্ন স্তরে পতনের সময় অতিরিক্ত শক্তি ফোটন (আলো) আকারে বিকিরণ করে: $h\nu \approx E_g$। ফলে নির্গত আলোর তরঙ্গদৈর্ঘ্য $\lambda \approx \frac{hc}{E_g}$ কেবল ব্যবহৃত সেমিকন্ডাক্টরের ব্যান্ডগ্যাপ $E_g$-এর ওপর নির্ভর করে।</t>
@@ -3204,11 +3029,6 @@
           <t>দৃশ্যমান বর্ণালীর লাল আলো ($\lambda \approx 700\text{ nm}$) থেকে বেগুনী আলো ($\lambda \approx 400\text{ nm}$) নিঃসরণকারী LED তৈরির জন্য সেমিকন্ডাক্টরের ব্যান্ডগ্যাপ $E_g$ কোন সীমার মধ্যে হতে হবে?</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>ব্যান্ডগ্যাপ শক্তি $E_g = \frac{hc}{\lambda} = \frac{1242\text{ eV}\cdot\text{nm}}{\lambda}$। লাল আলোর জন্য ($\lambda = 700\text{ nm}$): $E_{g,\min} = \frac{1242}{700} \approx 1.77\text{ eV} \approx 1.8\text{ eV}$। বেগুনী আলোর জন্য ($\lambda = 400\text{ nm}$): $E_{g,\max} = \frac{1242}{400} \approx 3.1\text{ eV}$। সুতরাং দৃশ্যমান আলোর LED তৈরির জন্য সেমিকন্ডাক্টরের ব্যান্ডগ্যাপ অবশ্যই প্রায় $1.8\text{ eV}$ থেকে $3.1\text{ eV}$-এর মধ্যে হতে হবে (যেমন GaAsP, GaN, InGaN)।</t>
@@ -3254,11 +3074,6 @@
           <t>ফটোডায়োড (Photodiode) সর্বদা বিপরীত বায়াসে (Reverse bias) চালিত হয় কেন? আলোক সংবেদনে এটি সম্মুখ বায়াস অপেক্ষা অধিক উপযোগী কেন?</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>সম্মুখ বায়াসে ডায়োডে মিলি-অ্যাম্পিয়ার স্তরের বিশাল সংখ্যাগুরু প্রবাহ থাকে, ফলে আলোর প্রভাবে সৃষ্ট অতি ক্ষুদ্র ফটো-বাহক মোট কারেন্টে কোনো লক্ষণীয় শতকরা পরিবর্তন ঘটাতে পারে না। কিন্তু বিপরীত বায়াসে কেবল অতি ক্ষুদ্র ন্যানো-অ্যাম্পিয়ার স্তরের অন্ধকার প্রবাহ ($I_{\text{dark}}$) থাকে। আলো পড়লে ডিপলেশন স্তরে সৃষ্ট অতিরিক্ত ইলেকট্রন-হোল জোড়ার কারণে বিপরীত কারেন্ট বহুগুণ ($100\%$ বা তার বেশি) বৃদ্ধি পায় যা ডিটেক্টরে অতি সহজে ও নিখুঁতভাবে পরিমাপ করা যায়। তাই ফটোডায়োড সর্বদা বিপরীত বায়াসে ব্যবহৃত হয়।</t>
@@ -3355,11 +3170,6 @@
           <t>সৌরকোষের ফিল ফ্যাক্টর (Fill Factor - FF) বলতে কী বোঝায় এবং এর সমীকরণটি লেখো। একটি আদর্শ সৌরকোষের সর্বোচ্চ আউটপুট ক্ষমতা কীভাবে নির্ধারিত হয়?</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>ফিল ফ্যাক্টর হলো সৌরকোষ থেকে প্রাপ্ত সর্বোচ্চ বাস্তব বৈদ্যুতিক ক্ষমতা ($P_{\max} = V_m I_m$) এবং উন্মুক্ত ভোল্টেজ ও শর্ট কারেন্টের তাত্ত্বিক গুণফলের ($V_{oc} I_{sc}$) অনুপাত: $FF = \frac{V_m I_m}{V_{oc} I_{sc}}$। এটি আই-ভি বক্ররেখার 'বর্গাকার' রূপ বা চমৎকারিত্বের পরিমাপক। ফিল ফ্যাক্টর যত ১-এর কাছাকাছি হয় (সাধারণত সিলিকনে $0.75-0.85$), সৌরকোষের রূপান্তর দক্ষতা তত বেশি হয়। সর্বোচ্চ ক্ষমতা $P_{\max} = FF \times V_{oc} \times I_{sc}$।</t>
@@ -3405,11 +3215,6 @@
           <t>ফটোডায়োডে কোনো আলো আপতিত না হওয়া সত্ত্বেও বিপরীত বায়াসে যে ক্ষুদ্র প্রবাহ থাকে তাকে কী বলে এবং এর উৎপত্তির কারণ কী?</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>কোনো আলো না থাকলে বিপরীত বায়াসে যে ক্ষুদ্র প্রবাহ প্রবাহিত হয় তাকে অন্ধকার প্রবাহ (Dark Current - $I_{\text{dark}}$) বলে। এটি মূলত সেমিকন্ডাক্টরের অভ্যন্তরীণ তাপীয় উত্তেজনার ফলে স্বতঃস্ফূর্তভাবে উৎপন্ন ইলেকট্রন-হোল যুগলের প্রবাহ (বিপরীত সম্পৃক্ত প্রবাহ)। তাপমাত্রা বৃদ্ধি পেলে বা বিপরীত ভোল্টেজ বাড়লে ডার্ক কারেন্ট বৃদ্ধি পায়, যা ডিটেক্টরের নয়েজ (শব্দ) সীমা নির্ধারণ করে।</t>
@@ -3455,11 +3260,6 @@
           <t>লেজার ডায়োডের (Laser Diode) সাথে সাধারণ LED-র মূল কার্যকরী পার্থক্য কী এবং এতে কোন কোয়ান্টাম ঘটনাটি কাজ করে?</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>সাধারণ LED স্বতঃস্ফূর্ত নিঃসরণ (Spontaneous Emission)-এর মাধ্যমে কাজ করে, ফলে নির্গত আলো অসম্বন্ধযুক্ত (Incoherent) ও তুলনামূলক চওড়া বর্ণালীযুক্ত হয়। লেজার ডায়োডে উচ্চ সম্মুখ কারেন্টে 'জনসংখ্যা বিপরীতকরণ' (Population Inversion) ঘটানো হয় এবং কেলাসের সমান্তরাল মসৃণ প্রতিফলক প্রান্তগুলোর মধ্যে অপটিক্যাল রেজোনেটর গহ্বর তৈরি করা হয়। ফলে আইনস্টাইনের উদ্দীপিত নিঃসরণ (Stimulated Emission) প্রক্রিয়ায় অত্যন্ত সুসংগত (Coherent), একবর্ণী ও তীব্র দিকমুখী লেজার রশ্মি নির্গত হয়।</t>
@@ -3505,11 +3305,6 @@
           <t>শর্টকি ডায়োড কীভাবে গঠিত হয় এবং সাধারণ $p-n$ জংশন ডায়োডের তুলনায় এর উচ্চ সুইচিং গতির কারণ কী?</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>শর্টকি ডায়োড একটি ধাতু (যেমন সোনা, প্ল্যাটিনাম বা সিলভার) এবং একটি হালকা ডোপড $n$-টাইপ সেমিকন্ডাক্টরের সংযোগে তৈরি হয় (Metal-Semiconductor Junction)। এতে কোনো $p$-টাইপ অঞ্চল থাকে না, ফলে বিদ্যুৎ প্রবাহ কেবল একক সংখ্যাগুরু বাহক (ইলেকট্রন) দ্বারা পরিচালিত হয়; কোনো সংখ্যালঘু বাহক নেই। সংখ্যালঘু বাহক না থাকায় এতে কোনো চার্জ সঞ্চয় (Stored minority charge) হয় না এবং রিভার্স রিকভারি সময় প্রায় শূন্য ($&lt; 100\text{ ps}$)। ফলে এটি গিগাহার্টজ কম্পাঙ্কের অতি দ্রুত সুইচিং এবং নিম্ন ভোল্টেজ ড্রপে ($0.2-0.3\text{ V}$) কাজ করে।</t>
@@ -3555,11 +3350,6 @@
           <t>সৌরকোষ তৈরির জন্য $E_g \approx 1.4-1.5\text{ eV}$ ব্যান্ডগ্যাপের উপাদান (যেমন GaAs বা CdTe) সবচেয়ে আদর্শ বলে বিবেচিত হয় কেন? শকলি-কোয়েসার সীমা (Shockley-Queisser Limit) ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>সৌর বর্ণালীতে শক্তি সর্বাধিক থাকে প্রায় ১.৫ eV ফোটনে। যদি ব্যান্ডগ্যাপ অতি বৃহৎ হয় ($E_g &gt; 2\text{ eV}$), তবে সূর্যের বেশিরভাগ ফোটন শোষিত না হয়ে পার হয়ে যায় (কারেন্ট কমে)। যদি ব্যান্ডগ্যাপ অতি ক্ষুদ্র হয় ($E_g &lt; 1\text{ eV}$), তবে প্রচুর ফোটন শোষিত হলেও অতিরিক্ত শক্তি ($h\nu - E_g$) তাপে নষ্ট হয় এবং উন্মুক্ত ভোল্টেজ $V_{oc}$ খুব কমে যায়। এই দুটি বিপরীতমুখী প্রভাবের সমন্বয়ে শকলি ও কোয়েসার (১৯৬১) দেখান যে একক জংশন সৌরকোষের তাত্ত্বিক সর্বোচ্চ দক্ষতা প্রায় ৩৩% হতে পারে কেবল যখন $E_g \approx 1.34-1.5\text{ eV}$ হয়।</t>
@@ -3605,11 +3395,6 @@
           <t>একটি পিন (PIN) ডায়োডের গঠনে $p$ এবং $n$ অঞ্চলের মাঝে কোন বিশেষ স্তর থাকে এবং এটি উচ্চ কম্পাঙ্কের আরএফ (RF) সুইচ হিসেবে কীভাবে কাজ করে?</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>PIN ডায়োডে ভারী ডোপড $p^+$ এবং $n^+$ অঞ্চলের মাঝে একটি চওড়া অভেদ্য সহজাত বা ইন্ট্রিনসিক (Intrinsic - $I$) স্তর থাকে। এই চওড়া $I$-স্তরের কারণে এর ডিপলেশন স্তর অনেক প্রশস্ত হয়, ফলে জংশন ধারকত্ব অত্যন্ত ক্ষুদ্র ($C \approx 0$) হয়। আরএফ (রেডিও কম্পাঙ্ক) সংকেতের ক্ষেত্রে বিপরীত বায়াসে এটি প্রায় নিখুঁত খোলা সুইচ বা উচ্চ রোধ প্রদর্শন করে। কিন্তু সম্মুখ বায়াসে $I$-স্তরে প্রচুর বাহক ইনজেক্ট হওয়ায় এটি একটি নিম্ন মান ও বিশুদ্ধ রৈখিক রোধকের মতো আচরণ করে যা আরএফ সিগন্যালকে অবিকৃতভাবে প্রবাহিত হতে দেয়।</t>
@@ -3639,12 +3424,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>সাধারণ নিঃসারক (CE) ট্রানজিস্টরের বিবর্ধন ও লোড রোধ</t>
+          <t>সেমিকন্ডাক্টর, ডায়োড, ট্রানজিস্টর ও সংখ্যা পদ্ধতি (Semiconductor &amp; Transistors)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -3652,31 +3437,25 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>##PRESET:bjt-npn[size:medium]##
-একটি সাধারণ নিঃসারক (CE) ট্রানজিস্টর বিবর্ধকে সংগ্রাহক লোড রোধ $R_L = 4.0\text{ k}\Omega$ এবং ইনপুট অভ্যন্তরীণ রোধ $R_{in} = 800\ \Omega$। ট্রানজিস্টরটির প্রবাহ বিবর্ধন গুণক $\alpha = 0.98$ হলে এর প্রবাহ লাভ ($\beta$), ভোল্টেজ বিবর্ধন ($A_v$) এবং ক্ষমতা লাভ ($A_p$) নির্ণয় কর।</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+কক্ষ তাপমাত্রায় ($300\text{ K}$) বিশুদ্ধ সিলিকনের অন্তর্নিহিত আধান বাহক ঘনত্ব $n_i = 1.5 \times 10^{16}\text{ m}^{-3}$। এতে প্রতি $10^6$ সিলিকন পরমাণুতে ১টি আর্সেনিক (পঞ্চযোজী) পরমাণু ডোপায়ন করা হলো। সিলিকনের পরমাণু ঘনত্ব $5.0 \times 10^{28}\text{ m}^{-3}$ হলে: (ক) নতুন ইলেকট্রন ঘনত্ব $n_e$, এবং (খ) ভর-ক্রিয়া সূত্রানুযায়ী হোল ঘনত্ব $n_h$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:bjt-npn[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>প্রবাহ লাভ: $\beta = \frac{\alpha}{1 - \alpha} = \frac{0.98}{1 - 0.98} = \frac{0.98}{0.02} = 49$।
-ভোল্টেজ লাভ: $A_v = \beta \times \frac{R_L}{R_{in}} = 49 \times \frac{4000}{800} = 49 \times 5 = 245$।
-ক্ষমতা লাভ: $A_p = \beta \times A_v = 49 \times 245 = 12005$।</t>
+          <t>দাতা ঘনত্ব $N_D = \frac{5.0 \times 10^{28}}{10^6} = 5.0 \times 10^{22}\text{ m}^{-3}$। যেহেতু $N_D \gg n_i$, তাই ইলেকট্রন ঘনত্ব $n_e \approx N_D = 5.0 \times 10^{22}\text{ m}^{-3}$। ভর-ক্রিয়া সূত্র (Mass Action Law): $n_e \cdot n_h = n_i^2 \implies n_h = \frac{n_i^2}{n_e} = \frac{(1.5 \times 10^{16})^2}{5.0 \times 10^{22}} = \frac{2.25 \times 10^{32}}{5.0 \times 10^{22}} = 4.5 \times 10^9\text{ m}^{-3}$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>$\beta = 49, A_v = 245, A_p = 12005$</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(ক) ইলেকট্রন ঘনত্ব $n_e = 5.0 \times 10^{22}\text{ m}^{-3}$, (খ) হোল ঘনত্ব $n_h = 4.5 \times 10^9\text{ m}^{-3}$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3696,12 +3475,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>জেনার ডায়োড ভোল্টেজ নিয়ন্ত্রক ও কারেন্ট বিভাজন</t>
+          <t>সেমিকন্ডাক্টর, ডায়োড, ট্রানজিস্টর ও সংখ্যা পদ্ধতি (Semiconductor &amp; Transistors)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3709,33 +3488,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##
-একটি জেনার ভোল্টেজ নিয়ন্ত্রক বর্তনীতে আনরেগুলেটেড ইনপুট ভোল্টেজ $V_{in} = 15\text{{ V}}$, জেনার ব্রেকডাউন ভোল্টেজ $V_Z = 9.0\text{{ V}}$, সিরিজ লিমিটিং রোধ $R_s = 200\ \Omega$ এবং লোড রোধ $R_L = 1.0\text{ k}\Omega$। সিরিজ রোধের মধ্য দিয়ে মোট প্রবাহ $I_s$, লোড প্রবাহ $I_L$, এবং জেনার প্রবাহ $I_Z$ নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি বিশুদ্ধ জার্মেনিয়াম ক্রিস্টালের প্রস্থচ্ছেদের ক্ষেত্রফল $A = 1.0\text{ cm}^2$ এবং দৈর্ঘ্য $L = 2.0\text{ mm}$। $300\text{ K}$ তাপমাত্রায় $n_i = 2.5 \times 10^{19}\text{ m}^{-3}$, ইলেকট্রন গতিশীলতা $\mu_e = 0.38\text{ m}^2/\text{V}\cdot\text{s}$ এবং হোল গতিশীলতা $\mu_h = 0.18\text{ m}^2/\text{V}\cdot\text{s}$ হলে ক্রিস্টালটির তড়িৎ পরিবাহিতা $\sigma$ এবং রোধ $R$ কত?</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>সিরিজ রোধের দুই প্রান্তে বিভব পতন $V_s = V_{in} - V_Z = 15 - 9 = 6\text{{ V}}$।
-মোট প্রবাহ $I_s = \frac{V_s}{R_s} = \frac{6}{200} = 0.030\text{{ A}} = 30\text{ mA}$।
-যেহেতু লোড জেনারের সাথে সমান্তরালে, তাই লোডের বিভব $V_L = V_Z = 9\text{{ V}}$।
-লোড প্রবাহ $I_L = \frac{V_Z}{R_L} = \frac{9}{1000} = 0.009\text{{ A}} = 9\text{ mA}$।
-কার্শফের সূত্রে জেনার প্রবাহ $I_Z = I_s - I_L = 30 - 9 = 21\text{ mA}$।</t>
+          <t>তড়িৎ পরিবাহিতা $\sigma = e n_i (\mu_e + \mu_h) = (1.6 \times 10^{-19}\text{ C}) \times (2.5 \times 10^{19}\text{ m}^{-3}) \times (0.38 + 0.18) = 4.0 \times 0.56 = 2.24\text{ S/m}$। আপেক্ষিক রোধ $\rho = \frac{1}{\sigma} = \frac{1}{2.24} \approx 0.4464\text{ }\Omega\cdot\text{m}$। ক্ষেত্রফল $A = 10^{-4}\text{ m}^2$, দৈর্ঘ্য $L = 2.0 \times 10^{-3}\text{ m}$। রোধ $R = \rho \frac{L}{A} = 0.4464 \times \frac{2.0 \times 10^{-3}}{10^{-4}} = 0.4464 \times 20 \approx 8.928\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>$I_s = 30\text{ mA}, I_L = 9\text{ mA}, I_Z = 21\text{ mA}$</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>পরিবাহিতা $\sigma = 2.24\text{ S/m} = 2.24\text{ }\Omega^{-1}\text{m}^{-1}$, রোধ $R = 8.93\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3755,7 +3526,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 3</t>
+          <t>সেমিকন্ডাক্টর, ডায়োড, ট্রানজিস্টর ও সংখ্যা পদ্ধতি (Semiconductor &amp; Transistors)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3764,28 +3535,29 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $13\text{ mA}$ হতে $33\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি সেমিকন্ডাক্টরের নিষিদ্ধ শক্তি ব্যবধান (Band gap) $E_g = 1.12\text{ eV}$ (সিলিকন)। ইলেকট্রনকে যোজন ব্যান্ড হতে পরিবহন ব্যান্ডে উন্নীত করতে কত সর্বোচ্চ তরঙ্গদৈর্ঘ্যের ফোটন শোষণ করতে হবে? এটি কি দৃশ্যমান আলোর অংশ?</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>ফোটনের শক্তি $E \ge E_g \implies \frac{h c}{\lambda_{\max}} = E_g \implies \lambda_{\max} = \frac{h c}{E_g} = \frac{1240\text{ eV}\cdot\text{nm}}{1.12\text{ eV}} \approx 1107.14\text{ nm} = 1.107\text{ }\mu\text{m}$। দৃশ্যমান আলোর সীমা ৭০০ ন্যানোমিটার পর্যন্ত হওয়ায় এই ফোটনটি অবলোহিত (IR) অঞ্চলের অন্তর্ভুক্ত।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>সর্বোচ্চ তরঙ্গদৈর্ঘ্য $\lambda_{\max} = 1107.1\text{ nm} = 1.107\\text{ }\mu\text{m}$ (অবলোহিত / Infrared অঞ্চলে)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3805,7 +3577,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 4</t>
+          <t>সেমিকন্ডাক্টর, ডায়োড, ট্রানজিস্টর ও সংখ্যা পদ্ধতি (Semiconductor &amp; Transistors)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3814,33 +3586,29 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##
-একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $14\text{ mA}$ হতে $34\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি ডায়োডের সম্মুখমুখী বায়াসে (Forward bias) ভোল্টেজ $0.65\text{ V}$ হতে সামান্য বৃদ্ধি করে $0.70\text{ V}$ করায় কারেন্ট $5.0\text{ mA}$ হতে বৃদ্ধি পেয়ে $25.0\text{ mA}$ হলো। ডায়োডটির গতিশীল রোধ (Dynamic resistance $r_d$) কত ওহম?</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>গতিশীল রোধের সমীকরণ: $r_d = \frac{\Delta V}{\Delta I} = \frac{0.70\text{ V} - 0.65\text{ V}}{25.0\text{ mA} - 5.0\text{ mA}} = \frac{0.05\text{ V}}{20.0 \times 10^{-3}\text{ A}} = \frac{0.05}{0.020} = 2.50\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>গতিশীল রোধ $r_d = 2.50\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3860,7 +3628,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 5</t>
+          <t>সেমিকন্ডাক্টর, ডায়োড, ট্রানজিস্টর ও সংখ্যা পদ্ধতি (Semiconductor &amp; Transistors)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,28 +3637,29 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $15\text{ mA}$ হতে $35\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি অর্ধ-তরঙ্গ একমুখীকারকে (Half-wave rectifier) $V_{	ext{rms}} = 20\text{ V}$ এসি ইনপুট সরবরাহ করা হলো। ডায়োডের সম্মুখ রোধ নগণ্য এবং লোড রোধ $R_L = 1000\text{ }\Omega$ হলে: (ক) ডিসি আউটপুট ভোল্টেজ $V_{	ext{dc}}$, এবং (খ) পিক ইনভার্স ভোল্টেজ (PIV) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>শীর্ষ ভোল্টেজ $V_m = \sqrt{2} V_{\text{rms}} = 1.4142 \times 20 = 28.284\text{ V}$। অর্ধ-তরঙ্গ একমুখীকারকে ডিসি ভোল্টেজ $V_{\text{dc}} = \frac{V_m}{\pi} = \frac{28.284}{\pi} \approx 9.003\text{ V}$। রিভার্স বায়াসে ডায়োডকে সর্বোচ্চ ভোল্টেজ সহ্য করতে হয়, তাই $\text{PIV} = V_m = 28.28\text{ V}$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(ক) $V_{\text{dc}} = 9.0\text{ V}$, (খ) $\text{PIV} = 28.28\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3910,7 +3679,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 6</t>
+          <t>সেমিকন্ডাক্টর, ডায়োড, ট্রানজিস্টর ও সংখ্যা পদ্ধতি (Semiconductor &amp; Transistors)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3919,28 +3688,29 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $16\text{ mA}$ হতে $36\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি পূর্ণ-তরঙ্গ ব্রিজ একমুখীকারকের (Full-wave bridge rectifier) সর্বোচ্চ তাত্ত্বিক একমুখীকরণ দক্ষতা $\eta_{\max} = 81.2\%$ প্রমাণ কর।</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>ডিসি আউটপুট ক্ষমতা $P_{\text{dc}} = I_{\text{dc}}^2 R_L = \left(\frac{2I_m}{\pi}\right)^2 R_L = \frac{4I_m^2 R_L}{\pi^2}$। এসি ইনপুট ক্ষমতা $P_{\text{ac}} = I_{\text{rms}}^2 R_L = \left(\frac{I_m}{\sqrt{2}}\right)^2 R_L = \frac{I_m^2 R_L}{2}$। দক্ষতা $\eta = \frac{P_{\text{dc}}}{P_{\text{ac}}} = \frac{\frac{4I_m^2 R_L}{\pi^2}}{\frac{I_m^2 R_L}{2}} = \frac{8}{\pi^2} \approx \frac{8}{9.8696} \approx 0.8106 \approx 81.2\%$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>সর্বোচ্চ দক্ষতা $\eta = \frac{8}{\pi^2} \approx 81.2\%$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3960,7 +3730,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 7</t>
+          <t>সেমিকন্ডাক্টর, ডায়োড, ট্রানজিস্টর ও সংখ্যা পদ্ধতি (Semiconductor &amp; Transistors)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3969,28 +3739,29 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $17\text{ mA}$ হতে $37\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি জেনার ডায়োড ভোল্টেজ নিয়ন্ত্রক বর্তনীতে ইনপুট ডিসি ভোল্টেজ $V_{	ext{in}} = 15.0\text{ V}$, জেনার ব্রেকডাউন ভোল্টেজ $V_Z = 9.0\text{ V}$, লোড রোধ $R_L = 1.0\text{ k}\Omega$, এবং জেনার কারেন্ট $I_Z = 10.0\text{ mA}$ হলে প্রয়োজনীয় শ্রেণি রোধক $R_s$-এর মান কত ওহম?</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>লোড কারেন্ট $I_L = \frac{V_Z}{R_L} = \frac{9.0\text{ V}}{1000\text{ }\Omega} = 9.0\text{ mA}$। মোট কারেন্ট $I = I_Z + I_L = 10.0\text{ mA} + 9.0\text{ mA} = 19.0\text{ mA} = 0.019\text{ A}$। শ্রেণি রোধের দুই প্রান্তে ভোল্টেজ পতন $V_s = V_{\text{in}} - V_Z = 15.0 - 9.0 = 6.0\text{ V}$। অতএব $R_s = \frac{V_s}{I} = \frac{6.0\text{ V}}{0.019\text{ A}} \approx 315.79\text{ }\Omega \approx 315.8\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>শ্রেণি রোধক $R_s = 315.8\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4010,7 +3781,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 8</t>
+          <t>সেমিকন্ডাক্টর, ডায়োড, ট্রানজিস্টর ও সংখ্যা পদ্ধতি (Semiconductor &amp; Transistors)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4019,33 +3790,29 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##
-একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $18\text{ mA}$ হতে $38\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি ট্রানজিস্টরের ক্ষেত্রে সাধারণ পিঠ (Common Base) কারেন্ট বিবর্ধন গুণক $lpha = 0.98$ হলে সাধারণ নিঃসারক (Common Emitter) কারেন্ট বিবর্ধন গুণক $eta$ কত? যদি বেস কারেন্ট $\Delta I_B = 20\text{ }\mu	ext{A}$ পরিবর্তিত হয়, তবে সংগ্রাহক কারেন্টের পরিবর্তন $\Delta I_C$ কত মিলি-অ্যাম্পিয়ার?</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>$\beta = \frac{\alpha}{1 - \alpha} = \frac{0.98}{1 - 0.98} = \frac{0.98}{0.02} = 49.0$। সংগ্রাহক কারেন্টের পরিবর্তন $\Delta I_C = \beta \Delta I_B = 49.0 \times (20 \times 10^{-6}\text{ A}) = 980 \times 10^{-6}\text{ A} = 0.98\text{ mA}$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>$\beta = 49.0$, সংগ্রাহক কারেন্ট পরিবর্তন $\Delta I_C = 0.98\text{ mA}$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4065,7 +3832,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 9</t>
+          <t>সেমিকন্ডাক্টর, ডায়োড, ট্রানজিস্টর ও সংখ্যা পদ্ধতি (Semiconductor &amp; Transistors)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4074,28 +3841,29 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $19\text{ mA}$ হতে $39\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি সাধারণ নিঃসারক (CE) ট্রানজিস্টর অ্যামপ্লিফায়ারে ইনপুট রোধ $R_{	ext{in}} = 1.0\text{ k}\Omega$, লোড রোধ $R_L = 5.0\text{ k}\Omega$ এবং $eta = 100$। অ্যামপ্লিফায়ারটির ভোল্টেজ লাভ ($A_v$) এবং ক্ষমতা লাভ ($A_p$) ডেসিবেলে (dB) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>ভোল্টেজ লাভ $A_v = \beta \frac{R_L}{R_{\text{in}}} = 100 \times \frac{5000}{1000} = 100 \times 5 = 500.0$। ডেসিবেলে ভোল্টেজ লাভ $= 20\log_{10}(500) = 20 \times 2.69897 \approx 53.98\text{ dB}$। ক্ষমতা লাভ $A_p = \beta A_v = 100 \times 500 = 50000.0$। ডেসিবেলে ক্ষমতা লাভ $= 10\log_{10}(50000) = 10 \times 4.69897 \approx 46.99\text{ dB}$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>ভোল্টেজ লাভ $A_v = 500.0$ ($53.98\text{ dB}$), ক্ষমতা লাভ $A_p = 50000.0$ ($46.99\text{ dB}$)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4115,7 +3883,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 10</t>
+          <t>সেমিকন্ডাক্টর, ডায়োড, ট্রানজিস্টর ও সংখ্যা পদ্ধতি (Semiconductor &amp; Transistors)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4124,28 +3892,29 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $20\text{ mA}$ হতে $40\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+দশমিক সংখ্যা $75_{10}$-কে বাইনারি, অক্টাল এবং হেক্সাডেসিমেল সংখ্যায় রূপান্তর কর।</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>বাইনারি রূপান্তর: $75 = 64 + 8 + 2 + 1 = 2^6 + 2^3 + 2^1 + 2^0 = 1001011_2$। অক্টাল রূপান্তর: $75 = 9 \times 8 + 3 = (1 \times 8 + 1) \times 8 + 3 = 113_8$ (বা ৩ বিট গ্রুপিং: $001 \ 001 \ 011 \to 113_8$)। হেক্সাডেসিমেল: $75 = 4 \times 16 + 11 = 4\text{B}_{16}$ (যেখানে $11 = \text{B}$)।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>বাইনারি $= 1001011_2$, অক্টাল $= 113_8$, হেক্সাডেসিমেল $= 4\text{B}_{16}$</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4165,37 +3934,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 11</t>
+          <t>লজিক গেট, বুলিয়ান বীজগণিত ও ডিমরগান সূত্র (Logic Gates &amp; Boolean Algebra)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $21\text{ mA}$ হতে $41\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+বুলিয়ান সমীকরণটি সরল কর: $Y = A B + A(B + C) + B(B + C)$। সরলীকৃত সমীকরণটি কোন মৌলিক লজিক গেট নির্দেশ করে?</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>$Y = A B + A B + A C + B \cdot B + B C$। বুলিয়ান নিয়ম $A B + A B = A B$ এবং $B \cdot B = B$: $Y = A B + A C + B + B C = A B + A C + B(1 + C)$। যেহেতু $1 + C = 1$, তাই $Y = A B + A C + B = B(1 + A) + A C = B(1) + A C = B + A C$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>সরলীকৃত সমীকরণ $Y = B + A C$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4215,42 +3985,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 12</t>
+          <t>লজিক গেট, বুলিয়ান বীজগণিত ও ডিমরগান সূত্র (Logic Gates &amp; Boolean Algebra)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##
-একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $22\text{ mA}$ হতে $42\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+ডি মরগানের দ্বিতীয় সূত্র $\overline{A \cdot B} = \overline{A} + \overline{B}$ টুথ টেবিল (Truth table) গঠনের মাধ্যমে প্রমাণ কর।</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>ইনপুট $(A, B)$ এর জন্য: (0,0) $\implies \overline{0\cdot 0} = 1$, $\overline{0} + \overline{0} = 1+1 = 1$; (0,1) $\implies \overline{0\cdot 1} = 1$, $1 + 0 = 1$; (1,0) $\implies \overline{1\cdot 0} = 1$, $0 + 1 = 1$; (1,1) $\implies \overline{1\cdot 1} = 0$, $0 + 0 = 0$। সমস্ত সম্ভাব্য অবস্থায় বামপক্ষ ও ডানপক্ষ অভিন্ন মান প্রদর্শন করায় ডিমরগানের সূত্র সর্বজনীন সত্য।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>উভয় পক্ষের সত্যক সারণির আউটপুট মান যথাক্রমে $[1, 1, 1, 0]$ হওয়ায় সূত্রটি প্রমাণিত</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4270,37 +4036,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 13</t>
+          <t>লজিক গেট, বুলিয়ান বীজগণিত ও ডিমরগান সূত্র (Logic Gates &amp; Boolean Algebra)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $23\text{ mA}$ হতে $43\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+কেন NAND গেট এবং NOR গেটকে সর্বজনীন গেট (Universal gates) বলা হয়? কেবল NAND গেট ব্যবহার করে কীভাবে একটি OR গেট তৈরি করা যায়?</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>OR অপারেশনের জন্য ডিমরগানের সূত্র: $A + B = \overline{\overline{A + B}} = \overline{\overline{A}\cdot\overline{B}}$। সুতরাং দুটি NAND গেটকে ইনভার্টার হিসেবে ব্যবহার করে $\overline{A}$ ও $\overline{B}$ তৈরি করা হয়, এবং এদের আউটপুটকে তৃতীয় একটি NAND গেটের ইনপুটে প্রবেশ করালে আউটপুটে $\overline{\overline{A}\cdot\overline{B}} = A + B$ পাওয়া যায়।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>এই গেটগুলোর যেকোনো একটি এককভাবে ব্যবহার করে অন্য যেকোনো মৌলিক গেট (AND, OR, NOT) তৈরি করা যায়; ২টি ইনভার্টার ও ১টি NAND দ্বারা OR গেট তৈরি হয়</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4320,37 +4087,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 14</t>
+          <t>লজিক গেট, বুলিয়ান বীজগণিত ও ডিমরগান সূত্র (Logic Gates &amp; Boolean Algebra)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $24\text{ mA}$ হতে $44\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি XOR গেটের বুলিয়ান সমীকরণ $Y = A \oplus B = \overline{A} B + A \overline{B}$। ইনপুট $A = 1$ এবং $B = 0$ হলে আউটপুট কত? সমরূপ দুটি ইনপুটের জন্য ($A = B$) XOR গেটের আউটপুট কী হয়?</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>$A = 1, B = 0$ হলে $Y = \overline{1}\cdot 0 + 1\cdot\overline{0} = 0\cdot 0 + 1\cdot 1 = 0 + 1 = 1$। সমরূপ ইনপুটে: $A = B = 1 \implies \overline{1}\cdot 1 + 1\cdot\overline{1} = 0 + 0 = 0$, এবং $A = B = 0 \implies \overline{0}\cdot 0 + 0\cdot\overline{0} = 0 + 0 = 0$। এ কারণে XOR গেটকে সমতা পরীক্ষক বা বিজোড় প্যারিটি ডিটেক্টর বলা হয়।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>$A=1, B=0$-তে আউটপুট $Y = 1$; সমরূপ ইনপুটে ($0,0$ বা $1,1$) আউটপুট সর্বদা $0$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4370,37 +4138,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 15</t>
+          <t>লজিক গেট, বুলিয়ান বীজগণিত ও ডিমরগান সূত্র (Logic Gates &amp; Boolean Algebra)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $25\text{ mA}$ হতে $45\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি ৪-বিট বাইনারি সংখ্যা $1011_2$-এর ২-এর পরিপূরক (2's complement) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>আদি সংখ্যা: $1011$। ১-এর পরিপূরক (বিট উল্টে): $0100$। ১ যোগ করে ২-এর পরিপূরক: $0100 + 1 = 0101_2$। (দশমিকে এটি $-5$ নির্দেশ করে)।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>২-এর পরিপূরক $= 0101_2$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4420,42 +4189,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 16</t>
+          <t>লজিক গেট, বুলিয়ান বীজগণিত ও ডিমরগান সূত্র (Logic Gates &amp; Boolean Algebra)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##
-একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $26\text{ mA}$ হতে $46\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি সৌর কোষের (Solar cell) ভোল্টেজ-কারেন্ট ($V-I$) বৈশিষ্ট্য লেখচিত্রের খোলা বর্তনী ভোল্টেজ $V_{	ext{oc}} = 0.60\text{ V}$ এবং শর্ট সার্কিট কারেন্ট $I_{	ext{sc}} = 40.0\text{ mA}$। সৌর কোষটির ফিল ফ্যাক্টর $FF = 0.75$ হলে এর সর্বোচ্চ আউটপুট ক্ষমতা $P_{\max}$ কত মিলিওয়াট?</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>ফিল ফ্যাক্টরের সমীকরণ: $FF = \frac{P_{\max}}{V_{\text{oc}} I_{\text{sc}}} \implies P_{\max} = FF \times V_{\text{oc}} \times I_{\text{sc}}$। মান বসিয়ে: $P_{\max} = 0.75 \times (0.60\text{ V}) \times (40.0\text{ mA}) = 0.75 \times 24.0\text{ mW} = 18.0\text{ mW}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>সর্বোচ্চ ক্ষমতা $P_{\max} = 18.0\text{ mW}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4475,37 +4240,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 17</t>
+          <t>লজিক গেট, বুলিয়ান বীজগণিত ও ডিমরগান সূত্র (Logic Gates &amp; Boolean Algebra)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $27\text{ mA}$ হতে $47\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+আলোক নিঃসারী ডায়োড (LED)-এর কার্যপ্রণালী: ফরোয়ার্ড বায়াসে LED কীভাবে আলো নির্গত করে এবং সিলিকন ডায়োড কেন দৃশ্যমান আলো বিকিরণে অক্ষম?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>ফরোয়ার্ড বায়াসে জাংশনে অতিরিক্ত ইলেকট্রন ও হোল প্রবেশ করে পরস্পরের সাথে পুনর্মিলিত (Recombination) হয়। গ্যালিয়াম আর্সেনাইড ফসফাইড ($\text{GaAsP}$) জাতীয় ডাইরেক্ট ব্যান্ড গ্যাপ সেমিকন্ডাক্টরে পুনর্মিলন শক্তি সরাসরি দৃশ্যমান ফোটন ($h f = E_g$) আকারে নির্গত হয়। কিন্তু সিলিকন ও জার্মেনিয়াম ইনডাইরেক্ট ব্যান্ড গ্যাপ হওয়ায় ভরবেগ সংরক্ষণে শক্তি মূলত ফোটনের বদলে তাপ ও ক্রিস্টাল কম্পনে রূপ নেয়।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>ইলেকট্রন ও হোলের পুনর্মিলনে ব্যান্ড গ্যাপ সমপরিমাণ শক্তি ফোটন আকারে মুক্ত হয়; সিলিকনে ইনডাইরেক্ট ব্যান্ড গ্যাপ থাকায় শক্তি ফোটন নয় জালিক কম্পনে (ফোনন / তাপে) নষ্ট হয়</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4525,37 +4291,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 18</t>
+          <t>লজিক গেট, বুলিয়ান বীজগণিত ও ডিমরগান সূত্র (Logic Gates &amp; Boolean Algebra)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $28\text{ mA}$ হতে $48\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি ট্রানজিস্টরে নিঃসারক কারেন্ট $I_E = 10.0\text{ mA}$ এবং বেস কারেন্ট $I_B = 100.0\text{ }\mu	ext{A}$। সংগ্রাহক কারেন্ট $I_C$ এবং কারেন্ট অনুপাত $lpha$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>ট্রানজিস্টরের কারেন্ট সমীকরণ: $I_E = I_B + I_C \implies I_C = I_E - I_B = 10.0\text{ mA} - 0.10\text{ mA} = 9.90\text{ mA}$। $\alpha = \frac{I_C}{I_E} = \frac{9.90\text{ mA}}{10.0\text{ mA}} = 0.990$।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>$I_C = 9.90\text{ mA}$, $\alpha = 0.990$</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4575,37 +4342,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 19</t>
+          <t>লজিক গেট, বুলিয়ান বীজগণিত ও ডিমরগান সূত্র (Logic Gates &amp; Boolean Algebra)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $29\text{ mA}$ হতে $49\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি সিই (CE) পরিবর্ধকে আউটপুট সিগন্যাল ইনপুট সিগন্যালের চেয়ে $180^\circ$ দশা পার্থক্য প্রদর্শন করে কেন?</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>আউটপুট সমীকরণ: $V_{CE} = V_{CC} - I_C R_L$। ইনপুট ধনাত্মক অর্ধচক্রে বেস কারেন্ট $I_B$ বৃদ্ধি পায়, ফলে সংগ্রাহক কারেন্ট $I_C$ বৃদ্ধি পায়। এর ফলে $I_C R_L$ বিভব পতন বেড়ে গিয়ে $V_{CE}$ ঋণাত্মক দিকে নেমে আসে। অর্থাৎ ইনপুটের ধনাত্মক চূড়ায় আউটপুটে ঋণাত্মক চূড়া গঠিত হয়, যা $180^\circ$ দশা পরিবর্তনের সৃষ্টি করে।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>ইনপুট ভোল্টেজ বৃদ্ধি পেলে বেস ও কালেক্টর কারেন্ট বাড়ে, ফলে লোড রোধে বিভব পতন বেড়ে কালেক্টর আউটপুট ভোল্টেজ হ্রাস পায়</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4625,42 +4393,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 20</t>
+          <t>লজিক গেট, বুলিয়ান বীজগণিত ও ডিমরগান সূত্র (Logic Gates &amp; Boolean Algebra)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##
-একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $30\text{ mA}$ হতে $50\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+বুলিয়ান সমীকরণটি বাস্তবায়ন কর: $Y = \overline{A + B \cdot C}$ কেবল NOR গেট ব্যবহার করে।</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>প্রদত্ত সমীকরণ $Y = \overline{A + BC}$। ডিমরগানের ১ম সূত্রানুসারে: $Y = \overline{A}\cdot \overline{BC} = \overline{A}\cdot (\overline{B} + \overline{C})$। সার্বজনীন NOR গেটের সাহায্যে প্রতিটি চলককে ইনভার্ট করে এবং সমান্তরাল NOR সমন্বয়ে এই লজিক সার্কিট তৈরি করা যায়।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>ডিমরগান সূত্র প্রয়োগে $Y = \overline{A}\cdot\overline{B\cdot C} = \overline{A}\cdot(\overline{B} + \overline{C})$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4680,37 +4444,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 21</t>
+          <t>উন্নত বর্তনী বিশ্লেষণ ও আধুনিক ইলেকট্রনিক্স (Advanced Electronics &amp; ICs)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $31\text{ mA}$ হতে $51\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি অর্ধ-তরঙ্গ এবং পূর্ণ-তরঙ্গ একমুখীকারকের রিপল ফ্যাক্টর (Ripple factor $\gamma$) যথাক্রমে কত এবং এর ভৌত অর্থ কী?</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>রিপল ফ্যাক্টরের সমীকরণ: $\gamma = \sqrt{\left(\frac{I_{\text{rms}}}{I_{\text{dc}}}\right)^2 - 1}$। অর্ধ-তরঙ্গে $\frac{I_{\text{rms}}}{I_{\text{dc}}} = \frac{I_m/2}{I_m/\pi} = \frac{\pi}{2} \approx 1.57 \implies \gamma = \sqrt{1.57^2 - 1} = \sqrt{1.467} \approx 1.21$। পূর্ণ-তরঙ্গে $\frac{I_{\text{rms}}}{I_{\text{dc}}} = \frac{I_m/\sqrt{2}}{2I_m/\pi} = \frac{\pi}{2\sqrt{2}} \approx 1.11 \implies \gamma = \sqrt{1.11^2 - 1} \approx 0.482$। পূর্ণ-তরঙ্গ আউটপুট অনেক বেশি মসৃণ ও কম খাঁজযুক্ত।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>অর্ধ-তরঙ্গে $\gamma = 1.21$, পূর্ণ-তরঙ্গে $\gamma = 0.482$; এটি আউটপুটে ডিসির তুলনায় অবশিষ্ট এসির অনুপাত নির্দেশ করে</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4730,37 +4495,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 22</t>
+          <t>উন্নত বর্তনী বিশ্লেষণ ও আধুনিক ইলেকট্রনিক্স (Advanced Electronics &amp; ICs)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $32\text{ mA}$ হতে $52\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি ফিল্টার বর্তনীতে ক্যাপাসিটর ফিল্টারের রিপল ভোল্টেজ সমীকরণ $V_{	ext{ripple}} = rac{I_{	ext{dc}}}{2 f C}$ (পূর্ণ-তরঙ্গে)। $f = 50\text{ Hz}$, $I_{	ext{dc}} = 100\text{ mA}$ এবং রিপল ভোল্টেজ $0.50\text{ V}$-এর নিচে রাখতে ধারকটির ন্যূনতম ধারকত্ব কত হতে হবে?</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>$V_r = \frac{I_{\text{dc}}}{2 f C} \implies C = \frac{I_{\text{dc}}}{2 f V_r} = \frac{100 \times 10^{-3}\text{ A}}{2(50\text{ s}^{-1})(0.50\text{ V})} = \frac{0.100}{50} = 2.0 \times 10^{-3}\text{ F} = 2000.0\text{ }\mu\text{F}$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>ন্যূনতম ধারকত্ব $C = 2000.0\text{ }\mu\text{F} = 2.0\text{ mF}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4780,37 +4546,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 23</t>
+          <t>উন্নত বর্তনী বিশ্লেষণ ও আধুনিক ইলেকট্রনিক্স (Advanced Electronics &amp; ICs)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $33\text{ mA}$ হতে $53\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি জেনার ডায়োড ভোল্টেজ নিয়ন্ত্রকের ইনপুট ভোল্টেজ $20\text{ V}$ হতে $30\text{ V}$ পর্যন্ত উঠানামা করে। $V_Z = 12.0\text{ V}, R_s = 500\text{ }\Omega$ এবং লোড রোধ $R_L = 1000\text{ }\Omega$। ইনপুট পরিবর্তনের সাথে জেনার কারেন্টের সর্বোচ্চ ও সর্বনিম্ন মান ($I_{Z,\min}$ ও $I_{Z,\max}$) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>লোড কারেন্ট সর্বদা ধ্রুব: $I_L = \frac{V_Z}{R_L} = \frac{12}{1000} = 12.0\text{ mA}$। যখন $V_{\text{in}} = 20\text{ V}$: মোট কারেন্ট $I_{\min} = \frac{20 - 12}{500} = \frac{8}{500} = 16.0\text{ mA} \implies I_{Z,\min} = 16 - 12 = 4.0\text{ mA}$। যখন $V_{\text{in}} = 30\text{ V}$: মোট কারেন্ট $I_{\max} = \frac{30 - 12}{500} = \frac{18}{500} = 36.0\text{ mA} \implies I_{Z,\max} = 36 - 12 = 24.0\text{ mA}$। সমস্ত অতিরিক্ত কারেন্ট জেনার ডায়োড দিয়ে প্রবাহিত হয়ে লোড ভোল্টেজকে স্থির রাখে।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>$I_{Z,\min} = 4.0\text{ mA}, I_{Z,\max} = 24.0\text{ mA}$, লোড ভোল্টেজ নিখুঁতভাবে $12.0\text{ V}$-এ স্থির থাকবে</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4830,42 +4597,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 24</t>
+          <t>উন্নত বর্তনী বিশ্লেষণ ও আধুনিক ইলেকট্রনিক্স (Advanced Electronics &amp; ICs)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##
-একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $34\text{ mA}$ হতে $54\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি ট্রানজিস্টরের বেস কারেন্ট $I_B = 50\text{ }\mu	ext{A}$ এবং কালেক্টর কারেন্ট $I_C = 4.95\text{ mA}$ হলে নিঃসরণ কারেন্ট $I_E$ এবং $lpha$ ও $eta$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>$I_E = I_B + I_C = 0.050\text{ mA} + 4.95\text{ mA} = 5.0\text{ mA}$। $\beta = \frac{I_C}{I_B} = \frac{4.95\text{ mA}}{0.050\text{ mA}} = 99.0$। $\alpha = \frac{I_C}{I_E} = \frac{4.95}{5.0} = 0.990$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>$I_E = 5.0\text{ mA}, \beta = 99.0, \alpha = 0.99$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4885,37 +4648,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 25</t>
+          <t>উন্নত বর্তনী বিশ্লেষণ ও আধুনিক ইলেকট্রনিক্স (Advanced Electronics &amp; ICs)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $35\text{ mA}$ হতে $55\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি ৪-ইনপুট NAND গেটের আউটপুট কখন '০' হবে এবং কখন '১' হবে?</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>NAND অপারেশন হলো AND-এর বিপরীত: $Y = \overline{A \cdot B \cdot C \cdot D}$। $A=B=C=D=1$ হলে $Y = \overline{1} = 0$। অন্য যেকোনো একটি বা একাধিক ইনপুট '০' হলে গুণফল '০' হয়, যার বিপরীত হয়ে আউটপুট '১' হবে।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>যখন ৪টি ইনপুটই একসাথে '১' হয় কেবল তখনই আউটপুট '০' হয়; অন্য সকল অবস্থায় আউটপুট '১' হবে</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4935,37 +4699,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 26</t>
+          <t>উন্নত বর্তনী বিশ্লেষণ ও আধুনিক ইলেকট্রনিক্স (Advanced Electronics &amp; ICs)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $36\text{ mA}$ হতে $56\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+অপারেশনাল অ্যামপ্লিফায়ার (Op-Amp)-এর ভার্চুয়াল গ্রাউন্ড (Virtual Ground) ধারণাটি কী? একটি ইনভার্টিং অ্যামপ্লিফায়ারে ইনপুট রোধ $R_1 = 10\text{ k}\Omega$ এবং ফিডব্যাক রোধ $R_f = 100\text{ k}\Omega$ হলে ভোল্টেজ গেইন $A_v$ কত?</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>নন-ইনভার্টিং প্রান্ত গ্রাউন্ডে ($0\text{ V}$) থাকলে ইনভার্টিং প্রান্তও কার্যত শূন্য বিভবে থাকে, যাকে ভার্চুয়াল গ্রাউন্ড বলে। ইনভার্টিং অ্যামপ্লিফায়ারের গেইন $A_v = -\frac{R_f}{R_1} = -\frac{100\text{ k}\Omega}{10\text{ k}\Omega} = -10.0$ (ঋণাত্মক চিহ্ন $180^\circ$ দশা পরিবর্তন নির্দেশ করে)।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>ভার্চুয়াল গ্রাউন্ড: অপ-অ্যাম্পের ওপেন লুপ গেইন প্রায় অসীম ($A \to \infty$) হওয়ায় ইনভার্টিং ও নন-ইনভার্টিং টার্মিনালের বিভব সমান থাকে; গেইন $A_v = -10.0$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4985,37 +4750,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 27</t>
+          <t>উন্নত বর্তনী বিশ্লেষণ ও আধুনিক ইলেকট্রনিক্স (Advanced Electronics &amp; ICs)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $37\text{ mA}$ হতে $57\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি বাইনারি পূর্ণ যোগক (Full Adder)-এর জন্য ৩টি ইনপুট বিট $A = 1, B = 1, C_{	ext{in}} = 1$ হলে যোগফল (Sum $S$) এবং ক্যারি (Carry $C_{	ext{out}}$) কত?</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>ফুল অ্যাডারের সমীকরণ: $S = A \oplus B \oplus C_{\text{in}} = 1 \oplus 1 \oplus 1 = 0 \oplus 1 = 1$। ক্যারি $C_{\text{out}} = A B + B C_{\text{in}} + A C_{\text{in}} = 1\cdot 1 + 1\cdot 1 + 1\cdot 1 = 1 + 1 + 1 = 1$। ফলে $S = 1, C_{\text{out}} = 1$।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>যোগফল $S = 1$, ক্যারি $C_{\text{out}} = 1$ (বাইনারিতে $1 + 1 + 1 = 11_2$)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5035,42 +4801,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 28</t>
+          <t>উন্নত বর্তনী বিশ্লেষণ ও আধুনিক ইলেকট্রনিক্স (Advanced Electronics &amp; ICs)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##
-একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $38\text{ mA}$ হতে $58\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি ট্রানজিস্টর সুইচ হিসেবে কাজ করার সময় কাট-অফ অঞ্চল (Cut-off region) এবং সম্পৃক্ত অঞ্চল (Saturation region)-এর আচরণ কীরূপ হয়?</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>বেস ভোল্টেজ কাট-ইন ভোল্টেজের নিচে থাকলে ($V_{BE} &lt; 0.7\text{ V}$) কোনো বেস কারেন্ট প্রবাহিত হয় না, ট্রানজিস্টর অফ থাকে (কাট-অফ), ফলে এটি একটি অফ সুইচের মতো অসীম রোধ সৃষ্টি করে। অন্যদিকে পর্যাপ্ত বেস কারেন্ট প্রয়োগ করলে ট্রানজিস্টর পূর্ণ সঞ্চালনশীল হয় (সম্পৃক্ত অবস্থা), কালেক্টর-নিঃসারক বিভব প্রায় শূন্যে নেমে আসে ($V_{CE} \approx 0$), এবং এটি একটি নিখুঁত অন সুইচের ন্যায় আচরণ করে।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>কাট-অফে ওপেন সুইচের ন্যায় কাজ করে ($I_C = 0, V_{CE} = V_{CC}$); সম্পৃক্ত অবস্থায় ক্লোজড সুইচের ন্যায় কাজ করে ($V_{CE} \approx 0.2\text{ V}, I_C$ সর্বোচ্চ)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5090,37 +4852,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 29</t>
+          <t>উন্নত বর্তনী বিশ্লেষণ ও আধুনিক ইলেকট্রনিক্স (Advanced Electronics &amp; ICs)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $39\text{ mA}$ হতে $59\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=4][size:small]##
+একটি এলইডি ডিসপ্লে সেগমেন্টে (Seven Segment Display) '8' সংখ্যাটি প্রদর্শন করতে কোন কোন সেগমেন্ট ($a, b, c, d, e, f, g$) প্রজ্বলিত করতে হবে এবং '0' প্রদর্শনে কোনটি বন্ধ থাকবে?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>সেভেন সেগমেন্ট ডিসপ্লেতে ৭টি এলইডি থাকে। '8' সংখ্যার ক্ষেত্রে সবকটি বাতি প্রজ্বলিত হয়। '0' প্রদর্শনে পরিধির ৬টি ($a, b, c, d, e, f$) অন থাকে এবং কেবল মাঝখানের অনুভূমিক $g$ সেগমেন্টটি বন্ধ রাখা হয়।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>'8' প্রদর্শনে সকল ৭টি সেগমেন্ট ($a,b,c,d,e,f,g$) অন থাকবে; '0' প্রদর্শনে মাঝের $g$ সেগমেন্টটি বন্ধ থাকবে</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5140,37 +4903,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 30</t>
+          <t>উন্নত বর্তনী বিশ্লেষণ ও আধুনিক ইলেকট্রনিক্স (Advanced Electronics &amp; ICs)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $40\text{ mA}$ হতে $60\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+আধুনিক ইন্টিগ্রেটেড সার্কিট (IC)-এর ক্ষুদ্রায়নে মুরের সূত্র (Moore's Law) বলতে কী বোঝায়?</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>ইন্টেল-এর সহ-প্রতিষ্ঠাতা গর্ডন মুর ১৯৬৫ সালে পর্যবেক্ষণ করেন যে সেমিকন্ডাক্টর ফ্যাব্রিকেশনের উন্নতির ফলে একই আয়তনের ইন্টিগ্রেটেড সার্কিট চিপে ট্রানজিস্টরের ঘনত্ব প্রতি ১৮ থেকে ২৪ মাসে প্রায় দ্বিগুণ হয়, যা অর্ধশতাব্দী ধরে কম্পিউটারের ক্ষমতা বহুগুণ বৃদ্ধি ও ব্যয় হ্রাসের মূল চালিকাশক্তি হিসেবে কাজ করেছে।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>প্রতি ১৮ হতে ২৪ মাসে একটি একক মাইক্রোচিপে ট্রানজিস্টরের সংখ্যা দ্বিগুণ হয়</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5190,37 +4954,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 31</t>
+          <t>উন্নত সেমিকন্ডাক্টর ও কোয়ান্টাম তথ্যপ্রযুক্তি (Advanced Semiconductor &amp; Quantum Info)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $41\text{ mA}$ হতে $61\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি বাইনারি বিয়োগ: ২-এর পরিপূরক পদ্ধতি ব্যবহার করে $28_{10} - 13_{10}$ সম্পাদন কর।</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>$28_{10} = 00011100_2$। $13_{10} = 00001101_2$। $-13$-এর ২-এর পরিপূরক: $11110010 + 1 = 11110011_2$। যোগ করে: $00011100 + 11110011 = (1)00001111_2$। অতিরিক্ত কেরি বিট বাদ দিলে থাকে $00001111_2 = 8 + 4 + 2 + 1 = 15_{10}$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>ফলাফল $= +15_{10} = 00001111_2$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5240,42 +5005,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 32</t>
+          <t>উন্নত সেমিকন্ডাক্টর ও কোয়ান্টাম তথ্যপ্রযুক্তি (Advanced Semiconductor &amp; Quantum Info)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##
-একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $42\text{ mA}$ হতে $62\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি সেমিকন্ডাক্টরের হোল ঘনত্ব $P = 5.0 	imes 10^{23}\text{ m}^{-3}$ এবং তাপমাত্রা বৃদ্ধি পাওয়ায় অভ্যন্তরীণ ঘনত্ব $n_i$ বেড়ে $1.0 	imes 10^{18}\text{ m}^{-3}$ হলো। নতুন ইলেকট্রন ঘনত্ব কত?</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>ভর-ক্রিয়া সূত্র: $n \cdot p = n_i^2 \implies n = \frac{n_i^2}{p} = \frac{(1.0 \times 10^{18})^2}{5.0 \times 10^{23}} = \frac{1.0 \times 10^{36}}{5.0 \times 10^{23}} = 2.0 \times 10^{12}\text{ m}^{-3}$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>ইলেকট্রন ঘনত্ব $n = 2.0 \times 10^{12}\text{ m}^{-3}$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5295,37 +5056,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 33</t>
+          <t>উন্নত সেমিকন্ডাক্টর ও কোয়ান্টাম তথ্যপ্রযুক্তি (Advanced Semiconductor &amp; Quantum Info)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $43\text{ mA}$ হতে $63\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি পি-এন জাংশনে নিঃশেষিত স্তরের (Depletion region) প্রস্থ $d = 0.50\text{ }\mu	ext{m}$ এবং রোধক বিভব (Barrier potential) $V_B = 0.70\text{ V}$ হলে জাংশনে গড়ে কত শক্তিশালী অভ্যন্তরীণ তড়িৎ ক্ষেত্র বিদ্যমান?</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>তড়িৎ ক্ষেত্র $E = \frac{V_B}{d} = \frac{0.70\text{ V}}{0.50 \times 10^{-6}\text{ m}} = 1.40 \times 10^6\text{ V/m}$। এই বিশাল ক্ষেত্রটিই অতিরিক্ত ইলেকট্রন ও হোলের স্বতঃস্ফূর্ত ব্যাপন প্রতিরোধ করে সাম্যাবস্থা রক্ষা করে।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>তড়িৎ ক্ষেত্র $E = 1.40 \times 10^6\text{ V/m}$ (প্রচণ্ড শক্তিশালী ক্ষেত্র)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5345,37 +5107,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 34</t>
+          <t>উন্নত সেমিকন্ডাক্টর ও কোয়ান্টাম তথ্যপ্রযুক্তি (Advanced Semiconductor &amp; Quantum Info)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $44\text{ mA}$ হতে $64\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি ট্রানজিস্টরে $lpha = 0.995$ হলে $eta$-এর মান কত?</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>$\beta = \frac{\alpha}{1 - \alpha} = \frac{0.995}{1 - 0.995} = \frac{0.995}{0.005} = 199.0$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>$\beta = 199.0$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5395,37 +5158,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 35</t>
+          <t>উন্নত সেমিকন্ডাক্টর ও কোয়ান্টাম তথ্যপ্রযুক্তি (Advanced Semiconductor &amp; Quantum Info)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $45\text{ mA}$ হতে $65\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি বুলিয়ান ফাংশন $F(A,B,C) = \sum(1, 3, 5, 7)$। কার্নো ম্যাপ (K-map) বা বুলিয়ান বীজগণিত দ্বারা সরলীকরণ কর।</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>মিনটার্মগুলো: $m_1 = \bar{A}\bar{B}C, m_3 = \bar{A}BC, m_5 = A\bar{B}C, m_7 = ABC$। $F = \bar{A}C(\bar{B} + B) + AC(\bar{B} + B) = \bar{A}C(1) + AC(1) = (\bar{A} + A)C = 1 \cdot C = C$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>সরলীকৃত সমীকরণ $F = C$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5445,42 +5209,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 36</t>
+          <t>উন্নত সেমিকন্ডাক্টর ও কোয়ান্টাম তথ্যপ্রযুক্তি (Advanced Semiconductor &amp; Quantum Info)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##
-একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $46\text{ mA}$ হতে $66\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি এন-পি-এন ট্রানজিস্টরে সংগ্রাহক সংযোগ সর্বদা বিপরীত বায়াসে রাখা হয় কেন?</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>এন-পি-এন ট্রানজিস্টরে মেজরিটি বাহক হলো ঋণাত্মক ইলেকট্রন যা নিঃসারক হতে ক্ষারিত হয়ে অত্যন্ত পাতলা বেস অতিক্রম করে সংগ্রাহক জাংশনে পৌঁছায়। সংগ্রাহকে ধনাত্মক বিভব (বিপরীত বায়াস) প্রয়োগ করলে এটি ইলেকট্রনগুলোকে তীব্রভাবে আকর্ষণ করে সংগ্রহ করে নেয়, ফলে কার্যকর বিবর্ধন সম্ভব হয়।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>নিঃসারক হতে ক্ষারিত মুক্ত ইলেকট্রনগুলোকে আকর্ষণ করে সংগ্রাহক বর্তনীতে সফলভাবে প্রবাহ নিশ্চিত করার জন্য</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5500,37 +5260,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 37</t>
+          <t>উন্নত সেমিকন্ডাক্টর ও কোয়ান্টাম তথ্যপ্রযুক্তি (Advanced Semiconductor &amp; Quantum Info)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $47\text{ mA}$ হতে $67\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি সৌর প্যানেলের ক্ষেত্রফল $2.0\text{ m}^2$ এবং এর রূপান্তর দক্ষতা $15\%$। সৌর বিকিরণের গড় তীব্রতা $1000\text{ W/m}^2$ হলে প্যানেলটির আউটপুট বৈদ্যুতিক ক্ষমতা কত ওয়াট?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>আপতিত মোট সৌর শক্তি $P_{\text{in}} = I \times A = 1000\text{ W/m}^2 \times 2.0\text{ m}^2 = 2000.0\text{ W}$। আউটপুট ক্ষমতা $P_{\text{out}} = \eta \times P_{\text{in}} = 0.15 \times 2000 = 300.0\text{ W}$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>আউটপুট ক্ষমতা $P = 300.0\text{ W}$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5550,37 +5311,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 38</t>
+          <t>উন্নত সেমিকন্ডাক্টর ও কোয়ান্টাম তথ্যপ্রযুক্তি (Advanced Semiconductor &amp; Quantum Info)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $48\text{ mA}$ হতে $68\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি সাধারণ নিঃসারক পরিবর্ধকে ইনপুট সিগন্যাল $V_i = 10\text{ mV}$ এবং ভোল্টেজ লাভ $80$। আউটপুট ভোল্টেজ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>$V_o = A_v \times V_i = 80 \times 10\text{ mV} = 800\text{ mV} = 0.80\text{ V}$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>আউটপুট ভোল্টেজ $V_o = 0.80\text{ V} = 800.0\text{ mV}$ ($180^\circ$ বিপরীত দশায়)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5600,37 +5362,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 39</t>
+          <t>উন্নত সেমিকন্ডাক্টর ও কোয়ান্টাম তথ্যপ্রযুক্তি (Advanced Semiconductor &amp; Quantum Info)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $49\text{ mA}$ হতে $69\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+ফটোগ্রাফিক সেন্সরে ব্যবহৃত চার্জ-কাপল্ড ডিভাইস (CCD) কোন নীতির ভিত্তিতে কাজ করে?</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>সিসিডি হলো লক্ষ লক্ষ ক্ষুদ্র ফটোডায়োডের একটি ম্যাট্রিক্স। আলোর ফোটন প্রতিটি পিক্সেলের সেমিকন্ডাক্টরে আঘাত করে আধান (ইলেকট্রন-হোল জোড়) সৃষ্টি করে যা স্থানীয় ক্যাপাসিটরে জমা হয়। এরপর একটি ক্লক পালসের মাধ্যমে আধানগুলো সারিবদ্ধভাবে স্থানান্তরিত হয়ে ডিজিটাল ভোল্টেজ সংকেতে রূপান্তরিত হয়।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>আলোক তড়িৎ ক্রিয়া এবং এমওএস (MOS) ক্যাপাসিটর নেটওয়ার্কে চার্জ স্থানান্তর নীতির ভিত্তিতে</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5650,42 +5413,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 40</t>
+          <t>উন্নত সেমিকন্ডাক্টর ও কোয়ান্টাম তথ্যপ্রযুক্তি (Advanced Semiconductor &amp; Quantum Info)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##
-একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $50\text{ mA}$ হতে $70\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+আধুনিক কোয়ান্টাম কম্পিউটিংয়ে ক্লাসিক্যাল বিট (০ ও ১) এবং কোয়ান্টাম কিউবিট (Qubit)-এর মধ্যকার মৌলিক পার্থক্য কী?</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>ক্লাসিক্যাল ট্রানজিস্টরে বিট কেবল দুটি স্বতন্ত্র অবস্থা ধারণ করে। কিন্তু একটি কিউবিট (যেমন ইলেকট্রনের স্পিন বা ফোটনের পোলারাইজেশন) যুগপৎ অসীম সংখ্যক দশায় সহাবস্থান করতে পারে। ফলে $N$ সংখ্যক কিউবিট একসাথে $2^N$ সংখ্যক সমান্তরাল গণনা পরিচালনা করতে সক্ষম, যা নির্দিষ্ট জটিল গাণিতিক সমস্যা সমাধানে চিরায়ত কম্পিউটারের চেয়ে কোটি গুণ দ্রুত কাজ করে।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>ক্লাসিক্যাল বিট নিশ্চিতভাবে ০ অথবা ১ নির্দেশ করে; কিউবিট কোয়ান্টাম উপরিপাতন (Superposition) নীতির ফলে একই সাথে ০ ও ১ এর রৈখিক সংমিশ্রণে থাকতে পারে ($|\psi\rangle = \alpha|0\rangle + \beta|1\rangle$)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5705,37 +5464,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 41</t>
+          <t>পি-এন জাংশন, পাওয়ার ইলেকট্রনিক্স ও ডিজিটাল সিস্টেম (PN Junctions &amp; Power Systems)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $51\text{ mA}$ হতে $71\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি পি-এন সিলিকন জাংশনে গ্রাহক ঘনত্ব $N_A = 10^{23}\text{ m}^{-3}$ এবং দাতা ঘনত্ব $N_D = 10^{22}\text{ m}^{-3}$। কক্ষ তাপমাত্রা $300\text{ K}$-এ অন্তর্নিহিত আধান ঘনত্ব $n_i = 1.5 \times 10^{16}\text{ m}^{-3}$ এবং তাপীয় বিভব $V_t = 0.026\text{ V}$ হলে জাংশনটির অভ্যন্তরীণ বিভব প্রাচীর (Built-in potential $V_{bi}$) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>অভ্যন্তরীণ বিভব প্রাচীরের সূত্র: $V_{bi} = V_t \ln\left(\frac{N_A N_D}{n_i^2}\right) = 0.026 \times \ln\left(\frac{10^{23} \times 10^{22}}{(1.5 \times 10^{16})^2}\right) = 0.026 \times \ln\left(\frac{10^{45}}{2.25 \times 10^{32}}\right) = 0.026 \times \ln(4.444 \times 10^{12}) = 0.026 \times 29.519 \approx 0.7675\text{ V}$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>অভ্যন্তরীণ বিভব প্রাচীর $V_{bi} = 0.767\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5755,37 +5515,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 42</t>
+          <t>পি-এন জাংশন, পাওয়ার ইলেকট্রনিক্স ও ডিজিটাল সিস্টেম (PN Junctions &amp; Power Systems)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $52\text{ mA}$ হতে $72\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি সাধারণ নিঃসারক (CE) ট্রানজিস্টর বর্তনীতে $V_{CC} = 12.0\text{ V}$ এবং সংগ্রাহক রোধ $R_C = 1.5\text{ k}\Omega$। ট্রানজিস্টরটির কিউ-বিন্দুতে (Q-point) সংগ্রাহক কারেন্ট $I_C = 4.0\text{ mA}$ হলে: (ক) সংগ্রাহক-নিঃসারক ভোল্টেজ $V_{CE}$, এবং (খ) ট্রানজিস্টরে ক্ষয়িত ক্ষমতা $P_D$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>$V_{CE} = V_{CC} - I_C R_C = 12.0 - (4.0 \times 10^{-3}\text{ A}) \times 1500\text{ }\Omega = 12.0 - 6.0 = 6.0\text{ V}$। ট্রানজিস্টরে ক্ষমতা ক্ষয় $P_D = V_{CE} I_C = 6.0\text{ V} \times 4.0\text{ mA} = 24.0\text{ mW}$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(ক) $V_{CE} = 6.0\text{ V}$, (খ) ক্ষয়িত ক্ষমতা $P_D = 24.0\text{ mW}$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5805,37 +5566,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 43</t>
+          <t>পি-এন জাংশন, পাওয়ার ইলেকট্রনিক্স ও ডিজিটাল সিস্টেম (PN Junctions &amp; Power Systems)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $53\text{ mA}$ হতে $73\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি জেনার ডায়োড ভোল্টেজ নিয়ন্ত্রক বর্তনীতে ইনপুট ভোল্টেজ $V_{\text{in}} = 24.0\text{ V}$, জেনার বিভব $V_Z = 10.0\text{ V}$, এবং সিরিজ রোধক $R_s = 200\text{ }\Omega$। যদি লোড রোধ $R_L$ পরিবর্তিত হয়ে $500\text{ }\Omega$ হতে $1000\text{ }\Omega$-এর মধ্যে থাকে, তবে জেনার ডায়োডে কারেন্টের সর্বনিম্ন ও সর্বোচ্চ মান ($I_{Z,\min}$ ও $I_{Z,\max}$) কত হবে?</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>সিরিজ কারেন্ট ধ্রুব: $I_s = \frac{V_{\text{in}} - V_Z}{R_s} = \frac{24.0 - 10.0}{200} = \frac{14.0}{200} = 0.070\text{ A} = 70.0\text{ mA}$। যখন $R_L = 500\text{ }\Omega$: $I_L = \frac{10}{500} = 20.0\text{ mA} \implies I_{Z,\min} = I_s - I_L = 70.0 - 20.0 = 50.0\text{ mA}$। যখন $R_L = 1000\text{ }\Omega$: $I_L = \frac{10}{1000} = 10.0\text{ mA} \implies I_{Z,\max} = 70.0 - 10.0 = 60.0\text{ mA}$।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>$I_{Z,\min} = 50.0\text{ mA}$ ($R_L = 500\text{ }\Omega$-তে), $I_{Z,\max} = 60.0\text{ mA}$ ($R_L = 1000\text{ }\Omega$-তে)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5855,42 +5617,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 44</t>
+          <t>পি-এন জাংশন, পাওয়ার ইলেকট্রনিক্স ও ডিজিটাল সিস্টেম (PN Junctions &amp; Power Systems)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##
-একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $54\text{ mA}$ হতে $74\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+ভগ্নাংশযুক্ত বাইনারি সংখ্যা $11010110.101_2$-কে দশমিক এবং অক্টাল সংখ্যা পদ্ধতিতে রূপান্তর কর।</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>পূর্ণাংশ: $11010110_2 = 128 + 64 + 16 + 4 + 2 = 214_{10}$। ভগ্নাংশ: $0.101_2 = 1\times 2^{-1} + 0\times 2^{-2} + 1\times 2^{-3} = 0.5 + 0.125 = 0.625_{10}$। সুতরাং দশমিক $= 214.625_{10}$। অক্টালে রূপান্তর (৩-বিট গ্রুপিং): $011 \ 010 \ 110 . 101 \implies 3 \ 2 \ 6 . 5 \implies 326.5_8$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>দশমিক $= 214.625_{10}$, অক্টাল $= 326.5_8$</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5910,37 +5668,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 45</t>
+          <t>পি-এন জাংশন, পাওয়ার ইলেকট্রনিক্স ও ডিজিটাল সিস্টেম (PN Junctions &amp; Power Systems)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $55\text{ mA}$ হতে $75\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+ডি মরগানের সূত্র প্রয়োগ করে বুলিয়ান সমীকরণটি সরল কর: $Y = \overline{(A + \overline{B}) \cdot (B + C)}$। $A = 1, B = 0, C = 1$ হলে আউটপুট মান কত?</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>ডি মরগানের ১ম সূত্র: $\overline{X \cdot Z} = \overline{X} + \overline{Z} \implies Y = \overline{A + \overline{B}} + \overline{B + C} = (\overline{A}\cdot\overline{\overline{B}}) + (\overline{B}\cdot\overline{C}) = \overline{A} B + \overline{B}\overline{C}$। মান বসালে ($A=1, B=0, C=1$): $Y = (\overline{1}\cdot 0) + (\overline{0}\cdot\overline{1}) = (0\cdot 0) + (1\cdot 0) = 0 + 0 = 0$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>সরলীকৃত সমীকরণ $Y = \\overline{A} B + \\overline{B}\\overline{C}$; আউটপুট $Y = 0$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5960,37 +5719,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 46</t>
+          <t>পি-এন জাংশন, পাওয়ার ইলেকট্রনিক্স ও ডিজিটাল সিস্টেম (PN Junctions &amp; Power Systems)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $56\text{ mA}$ হতে $76\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+কক্ষ তাপমাত্রায় তাপীয় বিভব $V_t = 26.0\text{ mV}$ এবং আদর্শতা গুণক $\eta = 1.0$। ডায়োড কারেন্ট সমীকরণ হতে প্রমাণ কর যে ফরোয়ার্ড বায়াসে গতিশীল রোধ $r_d = \frac{\eta V_t}{I}$। যদি ডায়োড কারেন্ট যথাক্রমে $2.0\text{ mA}$ এবং $10.0\text{ mA}$ হয়, তবে $r_d$-এর মান কত?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>$I \approx I_s e^{V/\eta V_t} \implies \frac{dI}{dV} = \frac{I_s e^{V/\eta V_t}}{\eta V_t} = \frac{I}{\eta V_t} \implies r_d = \frac{dV}{dI} = \frac{\eta V_t}{I}$। $I = 2.0\text{ mA}$-তে: $r_d = \frac{26.0\text{ mV}}{2.0\text{ mA}} = 13.0\text{ }\Omega$। $I = 10.0\text{ mA}$-তে: $r_d = \frac{26.0\text{ mV}}{10.0\text{ mA}} = 2.60\text{ }\Omega$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>$I = 2.0\text{ mA}$-তে $r_d = 13.0\text{ }\Omega$, $I = 10.0\text{ mA}$-তে $r_d = 2.60\text{ }\Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6010,37 +5770,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 47</t>
+          <t>পি-এন জাংশন, পাওয়ার ইলেকট্রনিক্স ও ডিজিটাল সিস্টেম (PN Junctions &amp; Power Systems)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $57\text{ mA}$ হতে $77\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি ট্রানজিস্টরের $\beta = 120$, ইনপুট রোধ $r_{\text{in}} = 800\text{ }\Omega$ এবং লোড রোধ $R_L = 4.0\text{ k}\Omega$। পরিবর্ধকটির ভোল্টেজ বিবর্ধন $A_v$, কারেন্ট বিবর্ধন $A_i$ এবং ক্ষমতা বিবর্ধন $A_p$ ডেসিবেলে (dB) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>$A_i = \beta = 120$। ভোল্টেজ বিবর্ধন $A_v = \beta \frac{R_L}{r_{\text{in}}} = 120 \times \frac{4000}{800} = 120 \times 5 = 600.0$। ডেসিবেলে ভোল্টেজ গেইন $= 20\log_{10}(600) \approx 55.56\text{ dB}$। ক্ষমতা বিবর্ধন $A_p = A_i A_v = 120 \times 600 = 72000.0$। ডেসিবেলে ক্ষমতা গেইন $= 10\log_{10}(72000) \approx 48.57\text{ dB}$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>$A_v = 600.0$ ($55.56\text{ dB}$), $A_i = 120.0$, ক্ষমতা বিবর্ধন $A_p = 72000.0$ ($48.57\text{ dB}$)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6060,42 +5821,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 48</t>
+          <t>পি-এন জাংশন, পাওয়ার ইলেকট্রনিক্স ও ডিজিটাল সিস্টেম (PN Junctions &amp; Power Systems)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##
-একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $58\text{ mA}$ হতে $78\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+শুধুমাত্র ২-ইনপুট NAND গেট ব্যবহার করে একটি হাফ অ্যাডার (Half Adder) তৈরি করতে ন্যূনতম কয়টি NAND গেটের প্রয়োজন? বর্তনীটির সংযোগ বিন্যাস ব্যাখ্যা কর।</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>##PRESET:zener-regulator[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>হাফ অ্যাডারের সমীকরণ: যোগফল $S = A \oplus B = (A + B)\overline{AB} = A\overline{AB} + B\overline{AB}$, এবং কেরি $C = AB$। ১ম NAND গেট ইনপুট $A$ ও $B$-কে নিয়ে $\overline{AB}$ তৈরি করে। ২য় ও ৩য় গেট যথাক্রমে $A$ ও $\overline{AB}$, এবং $B$ ও $\overline{AB}$-কে নিয়ে $\overline{A\overline{AB}}$ ও $\overline{B\overline{AB}}$ তৈরি করে। ৪র্থ গেট এদের সংযুক্ত করে যোগফল $S = A \oplus B$ প্রদান করে। ৫ম গেট ১ম গেটের আউটপুট $\overline{AB}$-কে ইনভার্ট করে কেরি $C = AB$ প্রদান করে। মোট ৫টি NAND গেট প্রয়োজন।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>ন্যূনতম ৫টি ২-ইনপুট NAND গেট প্রয়োজন</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6115,37 +5872,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 49</t>
+          <t>পি-এন জাংশন, পাওয়ার ইলেকট্রনিক্স ও ডিজিটাল সিস্টেম (PN Junctions &amp; Power Systems)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $59\text{ mA}$ হতে $79\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি $5.0\text{ cm} \times 5.0\text{ cm}$ আকারের সিলিকন সৌর কোষের ওপর $1000\text{ W/m}^2$ তীব্রতার সূর্যালোক আপতিত হয়। এর খোলা বর্তনী ভোল্টেজ $V_{\text{oc}} = 0.65\text{ V}$, শর্ট সার্কিট কারেন্ট $I_{\text{sc}} = 0.85\text{ A}$ এবং ফিল ফ্যাক্টর $FF = 0.78$ হলে কোষটির সর্বোচ্চ বৈদ্যুতিক আউটপুট ক্ষমতা এবং শক্তি রূপান্তর দক্ষতা $\eta$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>কোষের ক্ষেত্রফল $A = (0.05\text{ m}) \times (0.05\text{ m}) = 0.0025\text{ m}^2 = 2.5 \times 10^{-3}\text{ m}^2$। আপতিত মোট ক্ষমতা $P_{\text{in}} = I \times A = 1000 \times 0.0025 = 2.50\text{ W}$। সর্বোচ্চ আউটপুট ক্ষমতা $P_{\max} = FF \times V_{\text{oc}} \times I_{\text{sc}} = 0.78 \times 0.65\text{ V} \times 0.85\text{ A} \approx 0.43095\text{ W} \approx 431.0\text{ mW}$। দক্ষতা $\eta = \frac{P_{\max}}{P_{\text{in}}} \times 100\% = \frac{0.43095}{2.50} \times 100\% \approx 17.238\% \approx 17.24\%$।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>সর্বোচ্চ ক্ষমতা $P_{\max} = 0.431\text{ W} = 431.0\text{ mW}$, রূপান্তর দক্ষতা $\eta = 17.24\%$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6165,37 +5923,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>সেমিকন্ডাক্টর ডায়োড ও লজিক গেট বর্তনী 50</t>
+          <t>পি-এন জাংশন, পাওয়ার ইলেকট্রনিক্স ও ডিজিটাল সিস্টেম (PN Junctions &amp; Power Systems)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>একটি সিলিকন পি-এন জাংশন ডায়োডের বায়াস বিভব $0.65\text{ V}$ হতে $0.75\text{ V}$-এ বৃদ্ধি করলে সম্মুখী প্রবাহ $60\text{ mA}$ হতে $80\text{ mA}$-তে উন্নীত হয়। ডায়োডটির গতীয় রোধ ($r_d$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি পূর্ণ-তরঙ্গ ব্রিজ একমুখীকারকে ট্রান্সফরমারের গৌণ কুণ্ডলী হতে $24.0\text{ V}_{\text{rms}}, 50\text{ Hz}$ এসি ভোল্টেজ সরবরাহ করা হয়। লোড রোধ $R_L = 100\text{ }\Omega$ এবং এর সমান্তরালে $C = 1000\text{ }\mu\text{F}$ ফিল্টার ধারক সংযুক্ত। (ক) ডিসি লোড ভোল্টেজ $V_{\text{dc}}$, (খ) পিক-টু-পিক রিপল ভোল্টেজ $V_{r(pp)}$, এবং (গ) প্রতিটি ডায়োডের পিক ইনভার্স ভোল্টেজ (PIV) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>গতীয় রোধ $r_d = \frac{\Delta V}{\Delta I} = \frac{0.10\text{ V}}{20 \times 10^{-3}\text{ A}} = 5.0\ \Omega$।</t>
+          <t>শীর্ষ ভোল্টেজ $V_m = \sqrt{2} \times 24.0 \approx 33.94\text{ V}$। রিপল ভোল্টেজ $V_{r(pp)} = \frac{I_{\text{dc}}}{2 f C} \approx \frac{V_m}{2 f R_L C} = \frac{33.94}{2(50)(100)(1000 \times 10^{-6})} = \frac{33.94}{10.0} = 3.394\text{ V}$। ডিসি লোড ভোল্টেজ $V_{\text{dc}} = V_m - \frac{V_{r(pp)}}{2} = 33.94 - 1.697 \approx 32.24\text{ V}$। ব্রিজ একমুখীকারকে প্রতিটি ডায়োডের $\text{PIV} = V_m = 33.94\text{ V}$।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>$r_d = 5.0\ \Omega$</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>(ক) $V_{\text{dc}} \approx 32.25\text{ V}$, (খ) $V_{r(pp)} \approx 3.39\text{ V}$, (গ) $\text{PIV} = 33.94\text{ V}$</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
